--- a/model performance comparison/Amount_Cell_Media/Broeders 2015/Results/Fischer model_HepaRG.xlsx
+++ b/model performance comparison/Amount_Cell_Media/Broeders 2015/Results/Fischer model_HepaRG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAMU PHD\MassBalance project\New dataset from SOT poster\Broeders 2015\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAMU PHD\MassBalance project\Paper writing\R1\model comparison_update_based reviewer\New dataset from SOT poster\Broeders 2015\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23181C7A-9777-42FB-AF9F-CD07951F1DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8C8AC3-5E1F-49DD-A714-E047D4D88036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Model structure" sheetId="1" r:id="rId1"/>
@@ -1084,20 +1084,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="0.000000000"/>
-    <numFmt numFmtId="166" formatCode="0.00000000000"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="169" formatCode="0.00000_);[Red]\(0.00000\)"/>
-    <numFmt numFmtId="170" formatCode="0.000000_);[Red]\(0.000000\)"/>
-    <numFmt numFmtId="171" formatCode="0.0E+00"/>
+    <numFmt numFmtId="176" formatCode="0.000"/>
+    <numFmt numFmtId="177" formatCode="0.000000000"/>
+    <numFmt numFmtId="178" formatCode="0.00000000000"/>
+    <numFmt numFmtId="179" formatCode="0.0%"/>
+    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="181" formatCode="0.00000_);[Red]\(0.00000\)"/>
+    <numFmt numFmtId="182" formatCode="0.000000_);[Red]\(0.000000\)"/>
+    <numFmt numFmtId="183" formatCode="0.0E+00"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1214,13 +1214,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="3"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -1228,7 +1228,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1241,7 +1241,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1665,8 +1665,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="178" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1731,7 +1731,7 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1747,7 +1747,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1755,11 +1755,11 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1879,13 +1879,13 @@
     <xf numFmtId="2" fontId="1" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="180" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="20" fillId="8" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="181" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="182" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="182" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -1932,7 +1932,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1971,143 +1971,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2196,6 +2059,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2223,9 +2092,140 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="一般 2" xfId="1" xr:uid="{EAD913AB-B22E-45C0-B24F-41FAA7E034FC}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3401,7 +3401,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF297"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.5703125" customWidth="1"/>
     <col min="2" max="2" width="13.42578125" customWidth="1"/>
@@ -3414,7 +3414,7 @@
     <col min="22" max="22" width="29.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15.75" thickBot="1">
+    <row r="1" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -3448,7 +3448,7 @@
       <c r="AE1" s="7"/>
       <c r="AF1" s="7"/>
     </row>
-    <row r="2" spans="1:32" ht="18">
+    <row r="2" spans="1:32" ht="17.649999999999999" x14ac:dyDescent="0.5">
       <c r="A2" s="7"/>
       <c r="B2" s="115" t="s">
         <v>57</v>
@@ -3488,7 +3488,7 @@
       <c r="AE2" s="7"/>
       <c r="AF2" s="7"/>
     </row>
-    <row r="3" spans="1:32">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A3" s="7"/>
       <c r="B3" s="25" t="s">
         <v>0</v>
@@ -3526,7 +3526,7 @@
       <c r="AE3" s="7"/>
       <c r="AF3" s="7"/>
     </row>
-    <row r="4" spans="1:32" ht="15" customHeight="1" thickBot="1">
+    <row r="4" spans="1:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="7"/>
       <c r="B4" s="28"/>
       <c r="C4" s="29" t="s">
@@ -3562,7 +3562,7 @@
       <c r="AE4" s="7"/>
       <c r="AF4" s="7"/>
     </row>
-    <row r="5" spans="1:32" ht="15" customHeight="1">
+    <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="7"/>
       <c r="B5" s="20"/>
       <c r="C5" s="1"/>
@@ -3596,7 +3596,7 @@
       <c r="AE5" s="7"/>
       <c r="AF5" s="7"/>
     </row>
-    <row r="6" spans="1:32" ht="31.5" customHeight="1" thickBot="1">
+    <row r="6" spans="1:32" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="7"/>
       <c r="B6" s="22"/>
       <c r="C6" s="23"/>
@@ -3636,7 +3636,7 @@
       <c r="AE6" s="7"/>
       <c r="AF6" s="7"/>
     </row>
-    <row r="7" spans="1:32">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A7" s="7"/>
       <c r="B7" s="12"/>
       <c r="C7" s="7"/>
@@ -3676,7 +3676,7 @@
       <c r="AE7" s="7"/>
       <c r="AF7" s="7"/>
     </row>
-    <row r="8" spans="1:32" ht="15.75" thickBot="1">
+    <row r="8" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="7"/>
       <c r="B8" s="12"/>
       <c r="C8" s="7"/>
@@ -3716,7 +3716,7 @@
       <c r="AE8" s="7"/>
       <c r="AF8" s="7"/>
     </row>
-    <row r="9" spans="1:32">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A9" s="7"/>
       <c r="B9" s="12"/>
       <c r="C9" s="7"/>
@@ -3756,7 +3756,7 @@
       <c r="AE9" s="7"/>
       <c r="AF9" s="7"/>
     </row>
-    <row r="10" spans="1:32" ht="15.75" thickBot="1">
+    <row r="10" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="7"/>
       <c r="B10" s="12"/>
       <c r="C10" s="7"/>
@@ -3796,7 +3796,7 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="7"/>
     </row>
-    <row r="11" spans="1:32">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A11" s="7"/>
       <c r="B11" s="12"/>
       <c r="C11" s="7"/>
@@ -3836,7 +3836,7 @@
       <c r="AE11" s="7"/>
       <c r="AF11" s="7"/>
     </row>
-    <row r="12" spans="1:32">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A12" s="7"/>
       <c r="B12" s="12"/>
       <c r="C12" s="7"/>
@@ -3876,7 +3876,7 @@
       <c r="AE12" s="7"/>
       <c r="AF12" s="7"/>
     </row>
-    <row r="13" spans="1:32" ht="15.75" thickBot="1">
+    <row r="13" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="7"/>
       <c r="B13" s="12"/>
       <c r="C13" s="7"/>
@@ -3910,7 +3910,7 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="7"/>
     </row>
-    <row r="14" spans="1:32" ht="33" customHeight="1" thickBot="1">
+    <row r="14" spans="1:32" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="7"/>
       <c r="B14" s="12"/>
       <c r="C14" s="7"/>
@@ -3952,7 +3952,7 @@
       <c r="AE14" s="7"/>
       <c r="AF14" s="7"/>
     </row>
-    <row r="15" spans="1:32">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A15" s="7"/>
       <c r="B15" s="12"/>
       <c r="C15" s="7"/>
@@ -4001,7 +4001,7 @@
       <c r="AE15" s="7"/>
       <c r="AF15" s="7"/>
     </row>
-    <row r="16" spans="1:32" ht="15.75" thickBot="1">
+    <row r="16" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A16" s="7"/>
       <c r="B16" s="12"/>
       <c r="C16" s="7"/>
@@ -4043,7 +4043,7 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="7"/>
     </row>
-    <row r="17" spans="1:32">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A17" s="7"/>
       <c r="B17" s="12"/>
       <c r="C17" s="7"/>
@@ -4088,7 +4088,7 @@
       <c r="AE17" s="7"/>
       <c r="AF17" s="7"/>
     </row>
-    <row r="18" spans="1:32">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A18" s="7"/>
       <c r="B18" s="12"/>
       <c r="C18" s="7"/>
@@ -4130,7 +4130,7 @@
       <c r="AE18" s="7"/>
       <c r="AF18" s="7"/>
     </row>
-    <row r="19" spans="1:32" ht="15.75" thickBot="1">
+    <row r="19" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A19" s="7"/>
       <c r="B19" s="12"/>
       <c r="C19" s="7"/>
@@ -4172,7 +4172,7 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="7"/>
     </row>
-    <row r="20" spans="1:32" ht="15.75" thickBot="1">
+    <row r="20" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A20" s="7"/>
       <c r="B20" s="12"/>
       <c r="C20" s="7"/>
@@ -4206,7 +4206,7 @@
       <c r="AE20" s="7"/>
       <c r="AF20" s="7"/>
     </row>
-    <row r="21" spans="1:32">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A21" s="7"/>
       <c r="B21" s="12"/>
       <c r="C21" s="7"/>
@@ -4240,7 +4240,7 @@
       <c r="AE21" s="7"/>
       <c r="AF21" s="7"/>
     </row>
-    <row r="22" spans="1:32" ht="15.75" thickBot="1">
+    <row r="22" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A22" s="7"/>
       <c r="B22" s="12"/>
       <c r="C22" s="7"/>
@@ -4277,7 +4277,7 @@
       <c r="AE22" s="7"/>
       <c r="AF22" s="7"/>
     </row>
-    <row r="23" spans="1:32">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A23" s="7"/>
       <c r="B23" s="12"/>
       <c r="C23" s="7"/>
@@ -4311,7 +4311,7 @@
       <c r="AE23" s="7"/>
       <c r="AF23" s="7"/>
     </row>
-    <row r="24" spans="1:32" ht="15.75" thickBot="1">
+    <row r="24" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A24" s="7"/>
       <c r="B24" s="13"/>
       <c r="C24" s="24"/>
@@ -4345,7 +4345,7 @@
       <c r="AE24" s="7"/>
       <c r="AF24" s="7"/>
     </row>
-    <row r="25" spans="1:32" ht="15.75" thickBot="1">
+    <row r="25" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -4379,7 +4379,7 @@
       <c r="AE25" s="7"/>
       <c r="AF25" s="7"/>
     </row>
-    <row r="26" spans="1:32">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -4415,7 +4415,7 @@
       <c r="AE26" s="7"/>
       <c r="AF26" s="7"/>
     </row>
-    <row r="27" spans="1:32" ht="15.75" thickBot="1">
+    <row r="27" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -4454,7 +4454,7 @@
       <c r="AE27" s="7"/>
       <c r="AF27" s="7"/>
     </row>
-    <row r="28" spans="1:32">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -4493,7 +4493,7 @@
       <c r="AE28" s="7"/>
       <c r="AF28" s="7"/>
     </row>
-    <row r="29" spans="1:32">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -4526,7 +4526,7 @@
       <c r="AE29" s="7"/>
       <c r="AF29" s="7"/>
     </row>
-    <row r="30" spans="1:32">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -4560,7 +4560,7 @@
       <c r="AE30" s="7"/>
       <c r="AF30" s="7"/>
     </row>
-    <row r="31" spans="1:32" ht="15.75" thickBot="1">
+    <row r="31" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -4594,7 +4594,7 @@
       <c r="AE31" s="7"/>
       <c r="AF31" s="7"/>
     </row>
-    <row r="32" spans="1:32">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -4627,7 +4627,7 @@
       <c r="AE32" s="7"/>
       <c r="AF32" s="7"/>
     </row>
-    <row r="33" spans="1:32">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -4658,7 +4658,7 @@
       <c r="AE33" s="7"/>
       <c r="AF33" s="7"/>
     </row>
-    <row r="34" spans="1:32">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -4690,7 +4690,7 @@
       <c r="AE34" s="7"/>
       <c r="AF34" s="7"/>
     </row>
-    <row r="35" spans="1:32" ht="15.75" thickBot="1">
+    <row r="35" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -4724,7 +4724,7 @@
       <c r="AE35" s="7"/>
       <c r="AF35" s="7"/>
     </row>
-    <row r="36" spans="1:32">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -4756,7 +4756,7 @@
       <c r="AE36" s="7"/>
       <c r="AF36" s="7"/>
     </row>
-    <row r="37" spans="1:32">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -4789,7 +4789,7 @@
       <c r="AE37" s="7"/>
       <c r="AF37" s="7"/>
     </row>
-    <row r="38" spans="1:32">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -4823,7 +4823,7 @@
       <c r="AE38" s="7"/>
       <c r="AF38" s="7"/>
     </row>
-    <row r="39" spans="1:32" ht="15.75" thickBot="1">
+    <row r="39" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -4857,7 +4857,7 @@
       <c r="AE39" s="7"/>
       <c r="AF39" s="7"/>
     </row>
-    <row r="40" spans="1:32">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -4891,7 +4891,7 @@
       <c r="AE40" s="7"/>
       <c r="AF40" s="7"/>
     </row>
-    <row r="41" spans="1:32">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -4925,7 +4925,7 @@
       <c r="AE41" s="7"/>
       <c r="AF41" s="7"/>
     </row>
-    <row r="42" spans="1:32" ht="15.75" thickBot="1">
+    <row r="42" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -4959,7 +4959,7 @@
       <c r="AE42" s="7"/>
       <c r="AF42" s="7"/>
     </row>
-    <row r="43" spans="1:32">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
@@ -4993,7 +4993,7 @@
       <c r="AE43" s="7"/>
       <c r="AF43" s="7"/>
     </row>
-    <row r="44" spans="1:32">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -5027,7 +5027,7 @@
       <c r="AE44" s="7"/>
       <c r="AF44" s="7"/>
     </row>
-    <row r="45" spans="1:32">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -5061,7 +5061,7 @@
       <c r="AE45" s="7"/>
       <c r="AF45" s="7"/>
     </row>
-    <row r="46" spans="1:32" ht="15.75" thickBot="1">
+    <row r="46" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -5095,7 +5095,7 @@
       <c r="AE46" s="7"/>
       <c r="AF46" s="7"/>
     </row>
-    <row r="47" spans="1:32">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -5129,7 +5129,7 @@
       <c r="AE47" s="7"/>
       <c r="AF47" s="7"/>
     </row>
-    <row r="48" spans="1:32">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -5163,7 +5163,7 @@
       <c r="AE48" s="7"/>
       <c r="AF48" s="7"/>
     </row>
-    <row r="49" spans="1:32">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -5197,7 +5197,7 @@
       <c r="AE49" s="7"/>
       <c r="AF49" s="7"/>
     </row>
-    <row r="50" spans="1:32">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -5231,7 +5231,7 @@
       <c r="AE50" s="7"/>
       <c r="AF50" s="7"/>
     </row>
-    <row r="51" spans="1:32">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -5265,7 +5265,7 @@
       <c r="AE51" s="7"/>
       <c r="AF51" s="7"/>
     </row>
-    <row r="52" spans="1:32">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -5299,7 +5299,7 @@
       <c r="AE52" s="7"/>
       <c r="AF52" s="7"/>
     </row>
-    <row r="53" spans="1:32">
+    <row r="53" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
@@ -5333,7 +5333,7 @@
       <c r="AE53" s="7"/>
       <c r="AF53" s="7"/>
     </row>
-    <row r="54" spans="1:32">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
@@ -5367,7 +5367,7 @@
       <c r="AE54" s="7"/>
       <c r="AF54" s="7"/>
     </row>
-    <row r="55" spans="1:32">
+    <row r="55" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
@@ -5401,7 +5401,7 @@
       <c r="AE55" s="7"/>
       <c r="AF55" s="7"/>
     </row>
-    <row r="56" spans="1:32">
+    <row r="56" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
@@ -5435,7 +5435,7 @@
       <c r="AE56" s="7"/>
       <c r="AF56" s="7"/>
     </row>
-    <row r="57" spans="1:32">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
@@ -5469,7 +5469,7 @@
       <c r="AE57" s="7"/>
       <c r="AF57" s="7"/>
     </row>
-    <row r="58" spans="1:32">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
@@ -5503,7 +5503,7 @@
       <c r="AE58" s="7"/>
       <c r="AF58" s="7"/>
     </row>
-    <row r="59" spans="1:32">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
@@ -5537,7 +5537,7 @@
       <c r="AE59" s="7"/>
       <c r="AF59" s="7"/>
     </row>
-    <row r="60" spans="1:32">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
@@ -5571,7 +5571,7 @@
       <c r="AE60" s="7"/>
       <c r="AF60" s="7"/>
     </row>
-    <row r="61" spans="1:32">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A61" s="7"/>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
@@ -5605,7 +5605,7 @@
       <c r="AE61" s="7"/>
       <c r="AF61" s="7"/>
     </row>
-    <row r="62" spans="1:32">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
@@ -5639,7 +5639,7 @@
       <c r="AE62" s="7"/>
       <c r="AF62" s="7"/>
     </row>
-    <row r="63" spans="1:32">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
@@ -5673,7 +5673,7 @@
       <c r="AE63" s="7"/>
       <c r="AF63" s="7"/>
     </row>
-    <row r="64" spans="1:32">
+    <row r="64" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
@@ -5707,7 +5707,7 @@
       <c r="AE64" s="7"/>
       <c r="AF64" s="7"/>
     </row>
-    <row r="65" spans="1:32">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A65" s="7"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
@@ -5741,7 +5741,7 @@
       <c r="AE65" s="7"/>
       <c r="AF65" s="7"/>
     </row>
-    <row r="66" spans="1:32">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
@@ -5775,7 +5775,7 @@
       <c r="AE66" s="7"/>
       <c r="AF66" s="7"/>
     </row>
-    <row r="67" spans="1:32">
+    <row r="67" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
@@ -5809,7 +5809,7 @@
       <c r="AE67" s="7"/>
       <c r="AF67" s="7"/>
     </row>
-    <row r="68" spans="1:32">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
@@ -5843,7 +5843,7 @@
       <c r="AE68" s="7"/>
       <c r="AF68" s="7"/>
     </row>
-    <row r="69" spans="1:32">
+    <row r="69" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
@@ -5877,7 +5877,7 @@
       <c r="AE69" s="7"/>
       <c r="AF69" s="7"/>
     </row>
-    <row r="70" spans="1:32">
+    <row r="70" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
@@ -5911,7 +5911,7 @@
       <c r="AE70" s="7"/>
       <c r="AF70" s="7"/>
     </row>
-    <row r="71" spans="1:32">
+    <row r="71" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
@@ -5945,7 +5945,7 @@
       <c r="AE71" s="7"/>
       <c r="AF71" s="7"/>
     </row>
-    <row r="72" spans="1:32">
+    <row r="72" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
@@ -5979,7 +5979,7 @@
       <c r="AE72" s="7"/>
       <c r="AF72" s="7"/>
     </row>
-    <row r="73" spans="1:32">
+    <row r="73" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
@@ -6013,7 +6013,7 @@
       <c r="AE73" s="7"/>
       <c r="AF73" s="7"/>
     </row>
-    <row r="74" spans="1:32">
+    <row r="74" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
@@ -6047,7 +6047,7 @@
       <c r="AE74" s="7"/>
       <c r="AF74" s="7"/>
     </row>
-    <row r="75" spans="1:32">
+    <row r="75" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
@@ -6081,7 +6081,7 @@
       <c r="AE75" s="7"/>
       <c r="AF75" s="7"/>
     </row>
-    <row r="76" spans="1:32">
+    <row r="76" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
@@ -6115,7 +6115,7 @@
       <c r="AE76" s="7"/>
       <c r="AF76" s="7"/>
     </row>
-    <row r="77" spans="1:32">
+    <row r="77" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
@@ -6149,7 +6149,7 @@
       <c r="AE77" s="7"/>
       <c r="AF77" s="7"/>
     </row>
-    <row r="78" spans="1:32">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
@@ -6183,7 +6183,7 @@
       <c r="AE78" s="7"/>
       <c r="AF78" s="7"/>
     </row>
-    <row r="79" spans="1:32">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
@@ -6217,7 +6217,7 @@
       <c r="AE79" s="7"/>
       <c r="AF79" s="7"/>
     </row>
-    <row r="80" spans="1:32">
+    <row r="80" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
@@ -6251,7 +6251,7 @@
       <c r="AE80" s="7"/>
       <c r="AF80" s="7"/>
     </row>
-    <row r="81" spans="1:32">
+    <row r="81" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
@@ -6285,7 +6285,7 @@
       <c r="AE81" s="7"/>
       <c r="AF81" s="7"/>
     </row>
-    <row r="82" spans="1:32">
+    <row r="82" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
@@ -6319,7 +6319,7 @@
       <c r="AE82" s="7"/>
       <c r="AF82" s="7"/>
     </row>
-    <row r="83" spans="1:32">
+    <row r="83" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
@@ -6353,7 +6353,7 @@
       <c r="AE83" s="7"/>
       <c r="AF83" s="7"/>
     </row>
-    <row r="84" spans="1:32">
+    <row r="84" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
@@ -6387,7 +6387,7 @@
       <c r="AE84" s="7"/>
       <c r="AF84" s="7"/>
     </row>
-    <row r="85" spans="1:32">
+    <row r="85" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
@@ -6421,7 +6421,7 @@
       <c r="AE85" s="7"/>
       <c r="AF85" s="7"/>
     </row>
-    <row r="86" spans="1:32">
+    <row r="86" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -6455,7 +6455,7 @@
       <c r="AE86" s="7"/>
       <c r="AF86" s="7"/>
     </row>
-    <row r="87" spans="1:32">
+    <row r="87" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
@@ -6489,7 +6489,7 @@
       <c r="AE87" s="7"/>
       <c r="AF87" s="7"/>
     </row>
-    <row r="88" spans="1:32">
+    <row r="88" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
@@ -6523,7 +6523,7 @@
       <c r="AE88" s="7"/>
       <c r="AF88" s="7"/>
     </row>
-    <row r="89" spans="1:32">
+    <row r="89" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
@@ -6557,7 +6557,7 @@
       <c r="AE89" s="7"/>
       <c r="AF89" s="7"/>
     </row>
-    <row r="90" spans="1:32">
+    <row r="90" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
@@ -6591,7 +6591,7 @@
       <c r="AE90" s="7"/>
       <c r="AF90" s="7"/>
     </row>
-    <row r="91" spans="1:32">
+    <row r="91" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
@@ -6625,7 +6625,7 @@
       <c r="AE91" s="7"/>
       <c r="AF91" s="7"/>
     </row>
-    <row r="92" spans="1:32">
+    <row r="92" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
@@ -6659,7 +6659,7 @@
       <c r="AE92" s="7"/>
       <c r="AF92" s="7"/>
     </row>
-    <row r="93" spans="1:32">
+    <row r="93" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
@@ -6693,7 +6693,7 @@
       <c r="AE93" s="7"/>
       <c r="AF93" s="7"/>
     </row>
-    <row r="94" spans="1:32">
+    <row r="94" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
@@ -6727,7 +6727,7 @@
       <c r="AE94" s="7"/>
       <c r="AF94" s="7"/>
     </row>
-    <row r="95" spans="1:32">
+    <row r="95" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A95" s="7"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
@@ -6761,7 +6761,7 @@
       <c r="AE95" s="7"/>
       <c r="AF95" s="7"/>
     </row>
-    <row r="96" spans="1:32">
+    <row r="96" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
@@ -6795,7 +6795,7 @@
       <c r="AE96" s="7"/>
       <c r="AF96" s="7"/>
     </row>
-    <row r="97" spans="1:32">
+    <row r="97" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A97" s="7"/>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
@@ -6829,7 +6829,7 @@
       <c r="AE97" s="7"/>
       <c r="AF97" s="7"/>
     </row>
-    <row r="98" spans="1:32">
+    <row r="98" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
@@ -6863,7 +6863,7 @@
       <c r="AE98" s="7"/>
       <c r="AF98" s="7"/>
     </row>
-    <row r="99" spans="1:32">
+    <row r="99" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A99" s="7"/>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -6897,7 +6897,7 @@
       <c r="AE99" s="7"/>
       <c r="AF99" s="7"/>
     </row>
-    <row r="100" spans="1:32">
+    <row r="100" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
@@ -6931,7 +6931,7 @@
       <c r="AE100" s="7"/>
       <c r="AF100" s="7"/>
     </row>
-    <row r="101" spans="1:32">
+    <row r="101" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
@@ -6965,7 +6965,7 @@
       <c r="AE101" s="7"/>
       <c r="AF101" s="7"/>
     </row>
-    <row r="102" spans="1:32">
+    <row r="102" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -6999,7 +6999,7 @@
       <c r="AE102" s="7"/>
       <c r="AF102" s="7"/>
     </row>
-    <row r="103" spans="1:32">
+    <row r="103" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A103" s="7"/>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -7033,7 +7033,7 @@
       <c r="AE103" s="7"/>
       <c r="AF103" s="7"/>
     </row>
-    <row r="104" spans="1:32">
+    <row r="104" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -7067,7 +7067,7 @@
       <c r="AE104" s="7"/>
       <c r="AF104" s="7"/>
     </row>
-    <row r="105" spans="1:32">
+    <row r="105" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -7101,7 +7101,7 @@
       <c r="AE105" s="7"/>
       <c r="AF105" s="7"/>
     </row>
-    <row r="106" spans="1:32">
+    <row r="106" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -7135,7 +7135,7 @@
       <c r="AE106" s="7"/>
       <c r="AF106" s="7"/>
     </row>
-    <row r="107" spans="1:32">
+    <row r="107" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A107" s="7"/>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -7169,7 +7169,7 @@
       <c r="AE107" s="7"/>
       <c r="AF107" s="7"/>
     </row>
-    <row r="108" spans="1:32">
+    <row r="108" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -7203,7 +7203,7 @@
       <c r="AE108" s="7"/>
       <c r="AF108" s="7"/>
     </row>
-    <row r="109" spans="1:32">
+    <row r="109" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A109" s="7"/>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -7237,7 +7237,7 @@
       <c r="AE109" s="7"/>
       <c r="AF109" s="7"/>
     </row>
-    <row r="110" spans="1:32">
+    <row r="110" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -7271,7 +7271,7 @@
       <c r="AE110" s="7"/>
       <c r="AF110" s="7"/>
     </row>
-    <row r="111" spans="1:32">
+    <row r="111" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A111" s="7"/>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -7305,7 +7305,7 @@
       <c r="AE111" s="7"/>
       <c r="AF111" s="7"/>
     </row>
-    <row r="112" spans="1:32">
+    <row r="112" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -7339,7 +7339,7 @@
       <c r="AE112" s="7"/>
       <c r="AF112" s="7"/>
     </row>
-    <row r="113" spans="1:32">
+    <row r="113" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
       <c r="C113" s="7"/>
@@ -7373,7 +7373,7 @@
       <c r="AE113" s="7"/>
       <c r="AF113" s="7"/>
     </row>
-    <row r="114" spans="1:32">
+    <row r="114" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
       <c r="C114" s="7"/>
@@ -7407,7 +7407,7 @@
       <c r="AE114" s="7"/>
       <c r="AF114" s="7"/>
     </row>
-    <row r="115" spans="1:32">
+    <row r="115" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A115" s="7"/>
       <c r="B115" s="7"/>
       <c r="C115" s="7"/>
@@ -7441,7 +7441,7 @@
       <c r="AE115" s="7"/>
       <c r="AF115" s="7"/>
     </row>
-    <row r="116" spans="1:32">
+    <row r="116" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
       <c r="C116" s="7"/>
@@ -7475,7 +7475,7 @@
       <c r="AE116" s="7"/>
       <c r="AF116" s="7"/>
     </row>
-    <row r="117" spans="1:32">
+    <row r="117" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A117" s="7"/>
       <c r="B117" s="7"/>
       <c r="C117" s="7"/>
@@ -7509,7 +7509,7 @@
       <c r="AE117" s="7"/>
       <c r="AF117" s="7"/>
     </row>
-    <row r="118" spans="1:32">
+    <row r="118" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
       <c r="C118" s="7"/>
@@ -7543,7 +7543,7 @@
       <c r="AE118" s="7"/>
       <c r="AF118" s="7"/>
     </row>
-    <row r="119" spans="1:32">
+    <row r="119" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A119" s="7"/>
       <c r="B119" s="7"/>
       <c r="C119" s="7"/>
@@ -7577,7 +7577,7 @@
       <c r="AE119" s="7"/>
       <c r="AF119" s="7"/>
     </row>
-    <row r="120" spans="1:32">
+    <row r="120" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
       <c r="C120" s="7"/>
@@ -7611,7 +7611,7 @@
       <c r="AE120" s="7"/>
       <c r="AF120" s="7"/>
     </row>
-    <row r="121" spans="1:32">
+    <row r="121" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A121" s="7"/>
       <c r="B121" s="7"/>
       <c r="C121" s="7"/>
@@ -7645,7 +7645,7 @@
       <c r="AE121" s="7"/>
       <c r="AF121" s="7"/>
     </row>
-    <row r="122" spans="1:32">
+    <row r="122" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A122" s="7"/>
       <c r="B122" s="7"/>
       <c r="C122" s="7"/>
@@ -7679,7 +7679,7 @@
       <c r="AE122" s="7"/>
       <c r="AF122" s="7"/>
     </row>
-    <row r="123" spans="1:32">
+    <row r="123" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A123" s="7"/>
       <c r="B123" s="7"/>
       <c r="C123" s="7"/>
@@ -7713,7 +7713,7 @@
       <c r="AE123" s="7"/>
       <c r="AF123" s="7"/>
     </row>
-    <row r="124" spans="1:32">
+    <row r="124" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -7747,7 +7747,7 @@
       <c r="AE124" s="7"/>
       <c r="AF124" s="7"/>
     </row>
-    <row r="125" spans="1:32">
+    <row r="125" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -7781,7 +7781,7 @@
       <c r="AE125" s="7"/>
       <c r="AF125" s="7"/>
     </row>
-    <row r="126" spans="1:32">
+    <row r="126" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -7815,7 +7815,7 @@
       <c r="AE126" s="7"/>
       <c r="AF126" s="7"/>
     </row>
-    <row r="127" spans="1:32">
+    <row r="127" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -7849,7 +7849,7 @@
       <c r="AE127" s="7"/>
       <c r="AF127" s="7"/>
     </row>
-    <row r="128" spans="1:32">
+    <row r="128" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -7883,7 +7883,7 @@
       <c r="AE128" s="7"/>
       <c r="AF128" s="7"/>
     </row>
-    <row r="129" spans="1:32">
+    <row r="129" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -7917,7 +7917,7 @@
       <c r="AE129" s="7"/>
       <c r="AF129" s="7"/>
     </row>
-    <row r="130" spans="1:32">
+    <row r="130" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -7951,7 +7951,7 @@
       <c r="AE130" s="7"/>
       <c r="AF130" s="7"/>
     </row>
-    <row r="131" spans="1:32">
+    <row r="131" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -7985,7 +7985,7 @@
       <c r="AE131" s="7"/>
       <c r="AF131" s="7"/>
     </row>
-    <row r="132" spans="1:32">
+    <row r="132" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -8019,7 +8019,7 @@
       <c r="AE132" s="7"/>
       <c r="AF132" s="7"/>
     </row>
-    <row r="133" spans="1:32">
+    <row r="133" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -8053,7 +8053,7 @@
       <c r="AE133" s="7"/>
       <c r="AF133" s="7"/>
     </row>
-    <row r="134" spans="1:32">
+    <row r="134" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -8087,7 +8087,7 @@
       <c r="AE134" s="7"/>
       <c r="AF134" s="7"/>
     </row>
-    <row r="135" spans="1:32">
+    <row r="135" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -8121,7 +8121,7 @@
       <c r="AE135" s="7"/>
       <c r="AF135" s="7"/>
     </row>
-    <row r="136" spans="1:32">
+    <row r="136" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -8155,7 +8155,7 @@
       <c r="AE136" s="7"/>
       <c r="AF136" s="7"/>
     </row>
-    <row r="137" spans="1:32">
+    <row r="137" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -8189,7 +8189,7 @@
       <c r="AE137" s="7"/>
       <c r="AF137" s="7"/>
     </row>
-    <row r="138" spans="1:32">
+    <row r="138" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -8223,7 +8223,7 @@
       <c r="AE138" s="7"/>
       <c r="AF138" s="7"/>
     </row>
-    <row r="139" spans="1:32">
+    <row r="139" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -8257,7 +8257,7 @@
       <c r="AE139" s="7"/>
       <c r="AF139" s="7"/>
     </row>
-    <row r="140" spans="1:32">
+    <row r="140" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
@@ -8291,7 +8291,7 @@
       <c r="AE140" s="7"/>
       <c r="AF140" s="7"/>
     </row>
-    <row r="141" spans="1:32">
+    <row r="141" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A141" s="7"/>
       <c r="B141" s="7"/>
       <c r="C141" s="7"/>
@@ -8325,7 +8325,7 @@
       <c r="AE141" s="7"/>
       <c r="AF141" s="7"/>
     </row>
-    <row r="142" spans="1:32">
+    <row r="142" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A142" s="7"/>
       <c r="B142" s="7"/>
       <c r="C142" s="7"/>
@@ -8359,7 +8359,7 @@
       <c r="AE142" s="7"/>
       <c r="AF142" s="7"/>
     </row>
-    <row r="143" spans="1:32">
+    <row r="143" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A143" s="7"/>
       <c r="B143" s="7"/>
       <c r="C143" s="7"/>
@@ -8393,7 +8393,7 @@
       <c r="AE143" s="7"/>
       <c r="AF143" s="7"/>
     </row>
-    <row r="144" spans="1:32">
+    <row r="144" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A144" s="7"/>
       <c r="B144" s="7"/>
       <c r="C144" s="7"/>
@@ -8427,7 +8427,7 @@
       <c r="AE144" s="7"/>
       <c r="AF144" s="7"/>
     </row>
-    <row r="145" spans="1:32">
+    <row r="145" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A145" s="7"/>
       <c r="B145" s="7"/>
       <c r="C145" s="7"/>
@@ -8461,7 +8461,7 @@
       <c r="AE145" s="7"/>
       <c r="AF145" s="7"/>
     </row>
-    <row r="146" spans="1:32">
+    <row r="146" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
       <c r="C146" s="7"/>
@@ -8495,7 +8495,7 @@
       <c r="AE146" s="7"/>
       <c r="AF146" s="7"/>
     </row>
-    <row r="147" spans="1:32">
+    <row r="147" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A147" s="7"/>
       <c r="B147" s="7"/>
       <c r="C147" s="7"/>
@@ -8529,7 +8529,7 @@
       <c r="AE147" s="7"/>
       <c r="AF147" s="7"/>
     </row>
-    <row r="148" spans="1:32">
+    <row r="148" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A148" s="7"/>
       <c r="B148" s="7"/>
       <c r="C148" s="7"/>
@@ -8563,7 +8563,7 @@
       <c r="AE148" s="7"/>
       <c r="AF148" s="7"/>
     </row>
-    <row r="149" spans="1:32">
+    <row r="149" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A149" s="7"/>
       <c r="B149" s="7"/>
       <c r="C149" s="7"/>
@@ -8597,7 +8597,7 @@
       <c r="AE149" s="7"/>
       <c r="AF149" s="7"/>
     </row>
-    <row r="150" spans="1:32">
+    <row r="150" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A150" s="7"/>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
@@ -8631,7 +8631,7 @@
       <c r="AE150" s="7"/>
       <c r="AF150" s="7"/>
     </row>
-    <row r="151" spans="1:32">
+    <row r="151" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A151" s="7"/>
       <c r="B151" s="7"/>
       <c r="C151" s="7"/>
@@ -8665,7 +8665,7 @@
       <c r="AE151" s="7"/>
       <c r="AF151" s="7"/>
     </row>
-    <row r="152" spans="1:32">
+    <row r="152" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A152" s="7"/>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
@@ -8699,7 +8699,7 @@
       <c r="AE152" s="7"/>
       <c r="AF152" s="7"/>
     </row>
-    <row r="153" spans="1:32">
+    <row r="153" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A153" s="7"/>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
@@ -8733,7 +8733,7 @@
       <c r="AE153" s="7"/>
       <c r="AF153" s="7"/>
     </row>
-    <row r="154" spans="1:32">
+    <row r="154" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A154" s="7"/>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
@@ -8767,7 +8767,7 @@
       <c r="AE154" s="7"/>
       <c r="AF154" s="7"/>
     </row>
-    <row r="155" spans="1:32">
+    <row r="155" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A155" s="7"/>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
@@ -8801,7 +8801,7 @@
       <c r="AE155" s="7"/>
       <c r="AF155" s="7"/>
     </row>
-    <row r="156" spans="1:32">
+    <row r="156" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A156" s="7"/>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
@@ -8835,7 +8835,7 @@
       <c r="AE156" s="7"/>
       <c r="AF156" s="7"/>
     </row>
-    <row r="157" spans="1:32">
+    <row r="157" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A157" s="7"/>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -8869,7 +8869,7 @@
       <c r="AE157" s="7"/>
       <c r="AF157" s="7"/>
     </row>
-    <row r="158" spans="1:32">
+    <row r="158" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A158" s="7"/>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -8903,7 +8903,7 @@
       <c r="AE158" s="7"/>
       <c r="AF158" s="7"/>
     </row>
-    <row r="159" spans="1:32">
+    <row r="159" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A159" s="7"/>
       <c r="B159" s="7"/>
       <c r="C159" s="7"/>
@@ -8937,7 +8937,7 @@
       <c r="AE159" s="7"/>
       <c r="AF159" s="7"/>
     </row>
-    <row r="160" spans="1:32">
+    <row r="160" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A160" s="7"/>
       <c r="B160" s="7"/>
       <c r="C160" s="7"/>
@@ -8971,7 +8971,7 @@
       <c r="AE160" s="7"/>
       <c r="AF160" s="7"/>
     </row>
-    <row r="161" spans="1:32">
+    <row r="161" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A161" s="7"/>
       <c r="B161" s="7"/>
       <c r="C161" s="7"/>
@@ -9005,7 +9005,7 @@
       <c r="AE161" s="7"/>
       <c r="AF161" s="7"/>
     </row>
-    <row r="162" spans="1:32">
+    <row r="162" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A162" s="7"/>
       <c r="B162" s="7"/>
       <c r="C162" s="7"/>
@@ -9039,7 +9039,7 @@
       <c r="AE162" s="7"/>
       <c r="AF162" s="7"/>
     </row>
-    <row r="163" spans="1:32">
+    <row r="163" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A163" s="7"/>
       <c r="B163" s="7"/>
       <c r="C163" s="7"/>
@@ -9073,7 +9073,7 @@
       <c r="AE163" s="7"/>
       <c r="AF163" s="7"/>
     </row>
-    <row r="164" spans="1:32">
+    <row r="164" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A164" s="7"/>
       <c r="B164" s="7"/>
       <c r="C164" s="7"/>
@@ -9107,7 +9107,7 @@
       <c r="AE164" s="7"/>
       <c r="AF164" s="7"/>
     </row>
-    <row r="165" spans="1:32">
+    <row r="165" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A165" s="7"/>
       <c r="B165" s="7"/>
       <c r="C165" s="7"/>
@@ -9141,7 +9141,7 @@
       <c r="AE165" s="7"/>
       <c r="AF165" s="7"/>
     </row>
-    <row r="166" spans="1:32">
+    <row r="166" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A166" s="7"/>
       <c r="B166" s="7"/>
       <c r="C166" s="7"/>
@@ -9175,7 +9175,7 @@
       <c r="AE166" s="7"/>
       <c r="AF166" s="7"/>
     </row>
-    <row r="167" spans="1:32">
+    <row r="167" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A167" s="7"/>
       <c r="B167" s="7"/>
       <c r="C167" s="7"/>
@@ -9209,7 +9209,7 @@
       <c r="AE167" s="7"/>
       <c r="AF167" s="7"/>
     </row>
-    <row r="168" spans="1:32">
+    <row r="168" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A168" s="7"/>
       <c r="B168" s="7"/>
       <c r="C168" s="7"/>
@@ -9243,7 +9243,7 @@
       <c r="AE168" s="7"/>
       <c r="AF168" s="7"/>
     </row>
-    <row r="169" spans="1:32">
+    <row r="169" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A169" s="7"/>
       <c r="B169" s="7"/>
       <c r="C169" s="7"/>
@@ -9277,7 +9277,7 @@
       <c r="AE169" s="7"/>
       <c r="AF169" s="7"/>
     </row>
-    <row r="170" spans="1:32">
+    <row r="170" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A170" s="7"/>
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
@@ -9311,7 +9311,7 @@
       <c r="AE170" s="7"/>
       <c r="AF170" s="7"/>
     </row>
-    <row r="171" spans="1:32">
+    <row r="171" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A171" s="7"/>
       <c r="B171" s="7"/>
       <c r="C171" s="7"/>
@@ -9345,7 +9345,7 @@
       <c r="AE171" s="7"/>
       <c r="AF171" s="7"/>
     </row>
-    <row r="172" spans="1:32">
+    <row r="172" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A172" s="7"/>
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
@@ -9379,7 +9379,7 @@
       <c r="AE172" s="7"/>
       <c r="AF172" s="7"/>
     </row>
-    <row r="173" spans="1:32">
+    <row r="173" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A173" s="7"/>
       <c r="B173" s="7"/>
       <c r="C173" s="7"/>
@@ -9413,7 +9413,7 @@
       <c r="AE173" s="7"/>
       <c r="AF173" s="7"/>
     </row>
-    <row r="174" spans="1:32">
+    <row r="174" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A174" s="7"/>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
@@ -9447,7 +9447,7 @@
       <c r="AE174" s="7"/>
       <c r="AF174" s="7"/>
     </row>
-    <row r="175" spans="1:32">
+    <row r="175" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A175" s="7"/>
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
@@ -9481,7 +9481,7 @@
       <c r="AE175" s="7"/>
       <c r="AF175" s="7"/>
     </row>
-    <row r="176" spans="1:32">
+    <row r="176" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A176" s="7"/>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
@@ -9515,7 +9515,7 @@
       <c r="AE176" s="7"/>
       <c r="AF176" s="7"/>
     </row>
-    <row r="177" spans="1:32">
+    <row r="177" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A177" s="7"/>
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
@@ -9549,7 +9549,7 @@
       <c r="AE177" s="7"/>
       <c r="AF177" s="7"/>
     </row>
-    <row r="178" spans="1:32">
+    <row r="178" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A178" s="7"/>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
@@ -9583,7 +9583,7 @@
       <c r="AE178" s="7"/>
       <c r="AF178" s="7"/>
     </row>
-    <row r="179" spans="1:32">
+    <row r="179" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A179" s="7"/>
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
@@ -9617,7 +9617,7 @@
       <c r="AE179" s="7"/>
       <c r="AF179" s="7"/>
     </row>
-    <row r="180" spans="1:32">
+    <row r="180" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A180" s="7"/>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
@@ -9651,7 +9651,7 @@
       <c r="AE180" s="7"/>
       <c r="AF180" s="7"/>
     </row>
-    <row r="181" spans="1:32">
+    <row r="181" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A181" s="7"/>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
@@ -9685,7 +9685,7 @@
       <c r="AE181" s="7"/>
       <c r="AF181" s="7"/>
     </row>
-    <row r="182" spans="1:32">
+    <row r="182" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A182" s="7"/>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
@@ -9719,7 +9719,7 @@
       <c r="AE182" s="7"/>
       <c r="AF182" s="7"/>
     </row>
-    <row r="183" spans="1:32">
+    <row r="183" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A183" s="7"/>
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
@@ -9753,7 +9753,7 @@
       <c r="AE183" s="7"/>
       <c r="AF183" s="7"/>
     </row>
-    <row r="184" spans="1:32">
+    <row r="184" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A184" s="7"/>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
@@ -9787,7 +9787,7 @@
       <c r="AE184" s="7"/>
       <c r="AF184" s="7"/>
     </row>
-    <row r="185" spans="1:32">
+    <row r="185" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A185" s="7"/>
       <c r="B185" s="7"/>
       <c r="C185" s="7"/>
@@ -9821,7 +9821,7 @@
       <c r="AE185" s="7"/>
       <c r="AF185" s="7"/>
     </row>
-    <row r="186" spans="1:32">
+    <row r="186" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A186" s="7"/>
       <c r="B186" s="7"/>
       <c r="C186" s="7"/>
@@ -9855,7 +9855,7 @@
       <c r="AE186" s="7"/>
       <c r="AF186" s="7"/>
     </row>
-    <row r="187" spans="1:32">
+    <row r="187" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A187" s="7"/>
       <c r="B187" s="7"/>
       <c r="C187" s="7"/>
@@ -9889,7 +9889,7 @@
       <c r="AE187" s="7"/>
       <c r="AF187" s="7"/>
     </row>
-    <row r="188" spans="1:32">
+    <row r="188" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A188" s="7"/>
       <c r="B188" s="7"/>
       <c r="C188" s="7"/>
@@ -9923,7 +9923,7 @@
       <c r="AE188" s="7"/>
       <c r="AF188" s="7"/>
     </row>
-    <row r="189" spans="1:32">
+    <row r="189" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A189" s="7"/>
       <c r="B189" s="7"/>
       <c r="C189" s="7"/>
@@ -9957,7 +9957,7 @@
       <c r="AE189" s="7"/>
       <c r="AF189" s="7"/>
     </row>
-    <row r="190" spans="1:32">
+    <row r="190" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A190" s="7"/>
       <c r="B190" s="7"/>
       <c r="C190" s="7"/>
@@ -9991,7 +9991,7 @@
       <c r="AE190" s="7"/>
       <c r="AF190" s="7"/>
     </row>
-    <row r="191" spans="1:32">
+    <row r="191" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A191" s="7"/>
       <c r="B191" s="7"/>
       <c r="C191" s="7"/>
@@ -10025,7 +10025,7 @@
       <c r="AE191" s="7"/>
       <c r="AF191" s="7"/>
     </row>
-    <row r="192" spans="1:32">
+    <row r="192" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A192" s="7"/>
       <c r="B192" s="7"/>
       <c r="C192" s="7"/>
@@ -10059,7 +10059,7 @@
       <c r="AE192" s="7"/>
       <c r="AF192" s="7"/>
     </row>
-    <row r="193" spans="1:32">
+    <row r="193" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A193" s="7"/>
       <c r="B193" s="7"/>
       <c r="C193" s="7"/>
@@ -10093,7 +10093,7 @@
       <c r="AE193" s="7"/>
       <c r="AF193" s="7"/>
     </row>
-    <row r="194" spans="1:32">
+    <row r="194" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A194" s="7"/>
       <c r="B194" s="7"/>
       <c r="C194" s="7"/>
@@ -10127,7 +10127,7 @@
       <c r="AE194" s="7"/>
       <c r="AF194" s="7"/>
     </row>
-    <row r="195" spans="1:32">
+    <row r="195" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A195" s="7"/>
       <c r="B195" s="7"/>
       <c r="C195" s="7"/>
@@ -10161,7 +10161,7 @@
       <c r="AE195" s="7"/>
       <c r="AF195" s="7"/>
     </row>
-    <row r="196" spans="1:32">
+    <row r="196" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A196" s="7"/>
       <c r="B196" s="7"/>
       <c r="C196" s="7"/>
@@ -10195,7 +10195,7 @@
       <c r="AE196" s="7"/>
       <c r="AF196" s="7"/>
     </row>
-    <row r="197" spans="1:32">
+    <row r="197" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A197" s="7"/>
       <c r="B197" s="7"/>
       <c r="C197" s="7"/>
@@ -10229,7 +10229,7 @@
       <c r="AE197" s="7"/>
       <c r="AF197" s="7"/>
     </row>
-    <row r="198" spans="1:32">
+    <row r="198" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A198" s="7"/>
       <c r="B198" s="7"/>
       <c r="C198" s="7"/>
@@ -10263,7 +10263,7 @@
       <c r="AE198" s="7"/>
       <c r="AF198" s="7"/>
     </row>
-    <row r="199" spans="1:32">
+    <row r="199" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A199" s="7"/>
       <c r="B199" s="7"/>
       <c r="C199" s="7"/>
@@ -10297,7 +10297,7 @@
       <c r="AE199" s="7"/>
       <c r="AF199" s="7"/>
     </row>
-    <row r="200" spans="1:32">
+    <row r="200" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A200" s="7"/>
       <c r="B200" s="7"/>
       <c r="C200" s="7"/>
@@ -10331,7 +10331,7 @@
       <c r="AE200" s="7"/>
       <c r="AF200" s="7"/>
     </row>
-    <row r="201" spans="1:32">
+    <row r="201" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A201" s="7"/>
       <c r="B201" s="7"/>
       <c r="C201" s="7"/>
@@ -10365,7 +10365,7 @@
       <c r="AE201" s="7"/>
       <c r="AF201" s="7"/>
     </row>
-    <row r="202" spans="1:32">
+    <row r="202" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A202" s="7"/>
       <c r="B202" s="7"/>
       <c r="C202" s="7"/>
@@ -10399,7 +10399,7 @@
       <c r="AE202" s="7"/>
       <c r="AF202" s="7"/>
     </row>
-    <row r="203" spans="1:32">
+    <row r="203" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A203" s="7"/>
       <c r="B203" s="7"/>
       <c r="C203" s="7"/>
@@ -10433,7 +10433,7 @@
       <c r="AE203" s="7"/>
       <c r="AF203" s="7"/>
     </row>
-    <row r="204" spans="1:32">
+    <row r="204" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A204" s="7"/>
       <c r="B204" s="7"/>
       <c r="C204" s="7"/>
@@ -10467,7 +10467,7 @@
       <c r="AE204" s="7"/>
       <c r="AF204" s="7"/>
     </row>
-    <row r="205" spans="1:32">
+    <row r="205" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A205" s="7"/>
       <c r="B205" s="7"/>
       <c r="C205" s="7"/>
@@ -10501,7 +10501,7 @@
       <c r="AE205" s="7"/>
       <c r="AF205" s="7"/>
     </row>
-    <row r="206" spans="1:32">
+    <row r="206" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A206" s="7"/>
       <c r="B206" s="7"/>
       <c r="C206" s="7"/>
@@ -10535,7 +10535,7 @@
       <c r="AE206" s="7"/>
       <c r="AF206" s="7"/>
     </row>
-    <row r="207" spans="1:32">
+    <row r="207" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A207" s="7"/>
       <c r="B207" s="7"/>
       <c r="C207" s="7"/>
@@ -10569,7 +10569,7 @@
       <c r="AE207" s="7"/>
       <c r="AF207" s="7"/>
     </row>
-    <row r="208" spans="1:32">
+    <row r="208" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A208" s="7"/>
       <c r="B208" s="7"/>
       <c r="C208" s="7"/>
@@ -10603,7 +10603,7 @@
       <c r="AE208" s="7"/>
       <c r="AF208" s="7"/>
     </row>
-    <row r="209" spans="1:32">
+    <row r="209" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A209" s="7"/>
       <c r="B209" s="7"/>
       <c r="C209" s="7"/>
@@ -10637,7 +10637,7 @@
       <c r="AE209" s="7"/>
       <c r="AF209" s="7"/>
     </row>
-    <row r="210" spans="1:32">
+    <row r="210" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A210" s="7"/>
       <c r="B210" s="7"/>
       <c r="C210" s="7"/>
@@ -10671,7 +10671,7 @@
       <c r="AE210" s="7"/>
       <c r="AF210" s="7"/>
     </row>
-    <row r="211" spans="1:32">
+    <row r="211" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A211" s="7"/>
       <c r="B211" s="7"/>
       <c r="C211" s="7"/>
@@ -10705,7 +10705,7 @@
       <c r="AE211" s="7"/>
       <c r="AF211" s="7"/>
     </row>
-    <row r="212" spans="1:32">
+    <row r="212" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A212" s="7"/>
       <c r="B212" s="7"/>
       <c r="C212" s="7"/>
@@ -10739,7 +10739,7 @@
       <c r="AE212" s="7"/>
       <c r="AF212" s="7"/>
     </row>
-    <row r="213" spans="1:32">
+    <row r="213" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A213" s="7"/>
       <c r="B213" s="7"/>
       <c r="C213" s="7"/>
@@ -10773,7 +10773,7 @@
       <c r="AE213" s="7"/>
       <c r="AF213" s="7"/>
     </row>
-    <row r="214" spans="1:32">
+    <row r="214" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A214" s="7"/>
       <c r="B214" s="7"/>
       <c r="C214" s="7"/>
@@ -10807,7 +10807,7 @@
       <c r="AE214" s="7"/>
       <c r="AF214" s="7"/>
     </row>
-    <row r="215" spans="1:32">
+    <row r="215" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A215" s="7"/>
       <c r="B215" s="7"/>
       <c r="C215" s="7"/>
@@ -10841,7 +10841,7 @@
       <c r="AE215" s="7"/>
       <c r="AF215" s="7"/>
     </row>
-    <row r="216" spans="1:32">
+    <row r="216" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A216" s="7"/>
       <c r="B216" s="7"/>
       <c r="C216" s="7"/>
@@ -10875,7 +10875,7 @@
       <c r="AE216" s="7"/>
       <c r="AF216" s="7"/>
     </row>
-    <row r="217" spans="1:32">
+    <row r="217" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A217" s="7"/>
       <c r="B217" s="7"/>
       <c r="C217" s="7"/>
@@ -10909,7 +10909,7 @@
       <c r="AE217" s="7"/>
       <c r="AF217" s="7"/>
     </row>
-    <row r="218" spans="1:32">
+    <row r="218" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A218" s="7"/>
       <c r="B218" s="7"/>
       <c r="C218" s="7"/>
@@ -10943,7 +10943,7 @@
       <c r="AE218" s="7"/>
       <c r="AF218" s="7"/>
     </row>
-    <row r="219" spans="1:32">
+    <row r="219" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A219" s="7"/>
       <c r="B219" s="7"/>
       <c r="C219" s="7"/>
@@ -10977,7 +10977,7 @@
       <c r="AE219" s="7"/>
       <c r="AF219" s="7"/>
     </row>
-    <row r="220" spans="1:32">
+    <row r="220" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A220" s="7"/>
       <c r="B220" s="7"/>
       <c r="C220" s="7"/>
@@ -11011,7 +11011,7 @@
       <c r="AE220" s="7"/>
       <c r="AF220" s="7"/>
     </row>
-    <row r="221" spans="1:32">
+    <row r="221" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A221" s="7"/>
       <c r="B221" s="7"/>
       <c r="C221" s="7"/>
@@ -11045,7 +11045,7 @@
       <c r="AE221" s="7"/>
       <c r="AF221" s="7"/>
     </row>
-    <row r="222" spans="1:32">
+    <row r="222" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A222" s="7"/>
       <c r="B222" s="7"/>
       <c r="C222" s="7"/>
@@ -11079,7 +11079,7 @@
       <c r="AE222" s="7"/>
       <c r="AF222" s="7"/>
     </row>
-    <row r="223" spans="1:32">
+    <row r="223" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A223" s="7"/>
       <c r="B223" s="7"/>
       <c r="C223" s="7"/>
@@ -11113,7 +11113,7 @@
       <c r="AE223" s="7"/>
       <c r="AF223" s="7"/>
     </row>
-    <row r="224" spans="1:32">
+    <row r="224" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A224" s="7"/>
       <c r="B224" s="7"/>
       <c r="C224" s="7"/>
@@ -11147,7 +11147,7 @@
       <c r="AE224" s="7"/>
       <c r="AF224" s="7"/>
     </row>
-    <row r="225" spans="1:32">
+    <row r="225" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A225" s="7"/>
       <c r="B225" s="7"/>
       <c r="C225" s="7"/>
@@ -11181,7 +11181,7 @@
       <c r="AE225" s="7"/>
       <c r="AF225" s="7"/>
     </row>
-    <row r="226" spans="1:32">
+    <row r="226" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A226" s="7"/>
       <c r="B226" s="7"/>
       <c r="C226" s="7"/>
@@ -11215,7 +11215,7 @@
       <c r="AE226" s="7"/>
       <c r="AF226" s="7"/>
     </row>
-    <row r="227" spans="1:32">
+    <row r="227" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A227" s="7"/>
       <c r="B227" s="7"/>
       <c r="C227" s="7"/>
@@ -11249,7 +11249,7 @@
       <c r="AE227" s="7"/>
       <c r="AF227" s="7"/>
     </row>
-    <row r="228" spans="1:32">
+    <row r="228" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A228" s="7"/>
       <c r="B228" s="7"/>
       <c r="C228" s="7"/>
@@ -11283,7 +11283,7 @@
       <c r="AE228" s="7"/>
       <c r="AF228" s="7"/>
     </row>
-    <row r="229" spans="1:32">
+    <row r="229" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A229" s="7"/>
       <c r="B229" s="7"/>
       <c r="C229" s="7"/>
@@ -11317,7 +11317,7 @@
       <c r="AE229" s="7"/>
       <c r="AF229" s="7"/>
     </row>
-    <row r="230" spans="1:32">
+    <row r="230" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A230" s="7"/>
       <c r="B230" s="7"/>
       <c r="C230" s="7"/>
@@ -11351,7 +11351,7 @@
       <c r="AE230" s="7"/>
       <c r="AF230" s="7"/>
     </row>
-    <row r="231" spans="1:32">
+    <row r="231" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A231" s="7"/>
       <c r="B231" s="7"/>
       <c r="C231" s="7"/>
@@ -11385,7 +11385,7 @@
       <c r="AE231" s="7"/>
       <c r="AF231" s="7"/>
     </row>
-    <row r="232" spans="1:32">
+    <row r="232" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A232" s="7"/>
       <c r="B232" s="7"/>
       <c r="C232" s="7"/>
@@ -11419,7 +11419,7 @@
       <c r="AE232" s="7"/>
       <c r="AF232" s="7"/>
     </row>
-    <row r="233" spans="1:32">
+    <row r="233" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A233" s="7"/>
       <c r="B233" s="7"/>
       <c r="C233" s="7"/>
@@ -11453,7 +11453,7 @@
       <c r="AE233" s="7"/>
       <c r="AF233" s="7"/>
     </row>
-    <row r="234" spans="1:32">
+    <row r="234" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A234" s="7"/>
       <c r="B234" s="7"/>
       <c r="C234" s="7"/>
@@ -11487,7 +11487,7 @@
       <c r="AE234" s="7"/>
       <c r="AF234" s="7"/>
     </row>
-    <row r="235" spans="1:32">
+    <row r="235" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A235" s="7"/>
       <c r="B235" s="7"/>
       <c r="C235" s="7"/>
@@ -11521,7 +11521,7 @@
       <c r="AE235" s="7"/>
       <c r="AF235" s="7"/>
     </row>
-    <row r="236" spans="1:32">
+    <row r="236" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A236" s="7"/>
       <c r="B236" s="7"/>
       <c r="C236" s="7"/>
@@ -11555,7 +11555,7 @@
       <c r="AE236" s="7"/>
       <c r="AF236" s="7"/>
     </row>
-    <row r="237" spans="1:32">
+    <row r="237" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A237" s="7"/>
       <c r="B237" s="7"/>
       <c r="C237" s="7"/>
@@ -11589,7 +11589,7 @@
       <c r="AE237" s="7"/>
       <c r="AF237" s="7"/>
     </row>
-    <row r="238" spans="1:32">
+    <row r="238" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A238" s="7"/>
       <c r="B238" s="7"/>
       <c r="C238" s="7"/>
@@ -11623,7 +11623,7 @@
       <c r="AE238" s="7"/>
       <c r="AF238" s="7"/>
     </row>
-    <row r="239" spans="1:32">
+    <row r="239" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A239" s="7"/>
       <c r="B239" s="7"/>
       <c r="C239" s="7"/>
@@ -11657,7 +11657,7 @@
       <c r="AE239" s="7"/>
       <c r="AF239" s="7"/>
     </row>
-    <row r="240" spans="1:32">
+    <row r="240" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A240" s="7"/>
       <c r="B240" s="7"/>
       <c r="C240" s="7"/>
@@ -11691,7 +11691,7 @@
       <c r="AE240" s="7"/>
       <c r="AF240" s="7"/>
     </row>
-    <row r="241" spans="1:32">
+    <row r="241" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A241" s="7"/>
       <c r="B241" s="7"/>
       <c r="C241" s="7"/>
@@ -11725,7 +11725,7 @@
       <c r="AE241" s="7"/>
       <c r="AF241" s="7"/>
     </row>
-    <row r="242" spans="1:32">
+    <row r="242" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A242" s="7"/>
       <c r="B242" s="7"/>
       <c r="C242" s="7"/>
@@ -11759,7 +11759,7 @@
       <c r="AE242" s="7"/>
       <c r="AF242" s="7"/>
     </row>
-    <row r="243" spans="1:32">
+    <row r="243" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A243" s="7"/>
       <c r="B243" s="7"/>
       <c r="C243" s="7"/>
@@ -11793,7 +11793,7 @@
       <c r="AE243" s="7"/>
       <c r="AF243" s="7"/>
     </row>
-    <row r="244" spans="1:32">
+    <row r="244" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A244" s="7"/>
       <c r="B244" s="7"/>
       <c r="C244" s="7"/>
@@ -11827,7 +11827,7 @@
       <c r="AE244" s="7"/>
       <c r="AF244" s="7"/>
     </row>
-    <row r="245" spans="1:32">
+    <row r="245" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A245" s="7"/>
       <c r="B245" s="7"/>
       <c r="C245" s="7"/>
@@ -11861,7 +11861,7 @@
       <c r="AE245" s="7"/>
       <c r="AF245" s="7"/>
     </row>
-    <row r="246" spans="1:32">
+    <row r="246" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A246" s="7"/>
       <c r="B246" s="7"/>
       <c r="C246" s="7"/>
@@ -11895,7 +11895,7 @@
       <c r="AE246" s="7"/>
       <c r="AF246" s="7"/>
     </row>
-    <row r="247" spans="1:32">
+    <row r="247" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A247" s="7"/>
       <c r="B247" s="7"/>
       <c r="C247" s="7"/>
@@ -11929,7 +11929,7 @@
       <c r="AE247" s="7"/>
       <c r="AF247" s="7"/>
     </row>
-    <row r="248" spans="1:32">
+    <row r="248" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A248" s="7"/>
       <c r="B248" s="7"/>
       <c r="C248" s="7"/>
@@ -11963,7 +11963,7 @@
       <c r="AE248" s="7"/>
       <c r="AF248" s="7"/>
     </row>
-    <row r="249" spans="1:32">
+    <row r="249" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A249" s="7"/>
       <c r="B249" s="7"/>
       <c r="C249" s="7"/>
@@ -11997,7 +11997,7 @@
       <c r="AE249" s="7"/>
       <c r="AF249" s="7"/>
     </row>
-    <row r="250" spans="1:32">
+    <row r="250" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A250" s="7"/>
       <c r="B250" s="7"/>
       <c r="C250" s="7"/>
@@ -12031,7 +12031,7 @@
       <c r="AE250" s="7"/>
       <c r="AF250" s="7"/>
     </row>
-    <row r="251" spans="1:32">
+    <row r="251" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A251" s="7"/>
       <c r="B251" s="7"/>
       <c r="C251" s="7"/>
@@ -12065,7 +12065,7 @@
       <c r="AE251" s="7"/>
       <c r="AF251" s="7"/>
     </row>
-    <row r="252" spans="1:32">
+    <row r="252" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A252" s="7"/>
       <c r="B252" s="7"/>
       <c r="C252" s="7"/>
@@ -12099,7 +12099,7 @@
       <c r="AE252" s="7"/>
       <c r="AF252" s="7"/>
     </row>
-    <row r="253" spans="1:32">
+    <row r="253" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A253" s="7"/>
       <c r="B253" s="7"/>
       <c r="C253" s="7"/>
@@ -12133,7 +12133,7 @@
       <c r="AE253" s="7"/>
       <c r="AF253" s="7"/>
     </row>
-    <row r="254" spans="1:32">
+    <row r="254" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A254" s="7"/>
       <c r="B254" s="7"/>
       <c r="C254" s="7"/>
@@ -12167,7 +12167,7 @@
       <c r="AE254" s="7"/>
       <c r="AF254" s="7"/>
     </row>
-    <row r="255" spans="1:32">
+    <row r="255" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A255" s="7"/>
       <c r="B255" s="7"/>
       <c r="C255" s="7"/>
@@ -12201,7 +12201,7 @@
       <c r="AE255" s="7"/>
       <c r="AF255" s="7"/>
     </row>
-    <row r="256" spans="1:32">
+    <row r="256" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A256" s="7"/>
       <c r="B256" s="7"/>
       <c r="C256" s="7"/>
@@ -12235,7 +12235,7 @@
       <c r="AE256" s="7"/>
       <c r="AF256" s="7"/>
     </row>
-    <row r="257" spans="1:32">
+    <row r="257" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A257" s="7"/>
       <c r="B257" s="7"/>
       <c r="C257" s="7"/>
@@ -12269,7 +12269,7 @@
       <c r="AE257" s="7"/>
       <c r="AF257" s="7"/>
     </row>
-    <row r="258" spans="1:32">
+    <row r="258" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A258" s="7"/>
       <c r="B258" s="7"/>
       <c r="C258" s="7"/>
@@ -12303,7 +12303,7 @@
       <c r="AE258" s="7"/>
       <c r="AF258" s="7"/>
     </row>
-    <row r="259" spans="1:32">
+    <row r="259" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A259" s="7"/>
       <c r="B259" s="7"/>
       <c r="C259" s="7"/>
@@ -12337,7 +12337,7 @@
       <c r="AE259" s="7"/>
       <c r="AF259" s="7"/>
     </row>
-    <row r="260" spans="1:32">
+    <row r="260" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A260" s="7"/>
       <c r="B260" s="7"/>
       <c r="C260" s="7"/>
@@ -12371,7 +12371,7 @@
       <c r="AE260" s="7"/>
       <c r="AF260" s="7"/>
     </row>
-    <row r="261" spans="1:32">
+    <row r="261" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A261" s="7"/>
       <c r="B261" s="7"/>
       <c r="C261" s="7"/>
@@ -12405,7 +12405,7 @@
       <c r="AE261" s="7"/>
       <c r="AF261" s="7"/>
     </row>
-    <row r="262" spans="1:32">
+    <row r="262" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A262" s="7"/>
       <c r="B262" s="7"/>
       <c r="C262" s="7"/>
@@ -12439,7 +12439,7 @@
       <c r="AE262" s="7"/>
       <c r="AF262" s="7"/>
     </row>
-    <row r="263" spans="1:32">
+    <row r="263" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A263" s="7"/>
       <c r="B263" s="7"/>
       <c r="C263" s="7"/>
@@ -12473,7 +12473,7 @@
       <c r="AE263" s="7"/>
       <c r="AF263" s="7"/>
     </row>
-    <row r="264" spans="1:32">
+    <row r="264" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A264" s="7"/>
       <c r="B264" s="7"/>
       <c r="C264" s="7"/>
@@ -12507,7 +12507,7 @@
       <c r="AE264" s="7"/>
       <c r="AF264" s="7"/>
     </row>
-    <row r="265" spans="1:32">
+    <row r="265" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A265" s="7"/>
       <c r="B265" s="7"/>
       <c r="C265" s="7"/>
@@ -12541,7 +12541,7 @@
       <c r="AE265" s="7"/>
       <c r="AF265" s="7"/>
     </row>
-    <row r="266" spans="1:32">
+    <row r="266" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A266" s="7"/>
       <c r="B266" s="7"/>
       <c r="C266" s="7"/>
@@ -12575,7 +12575,7 @@
       <c r="AE266" s="7"/>
       <c r="AF266" s="7"/>
     </row>
-    <row r="267" spans="1:32">
+    <row r="267" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A267" s="7"/>
       <c r="B267" s="7"/>
       <c r="C267" s="7"/>
@@ -12609,7 +12609,7 @@
       <c r="AE267" s="7"/>
       <c r="AF267" s="7"/>
     </row>
-    <row r="268" spans="1:32">
+    <row r="268" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A268" s="7"/>
       <c r="B268" s="7"/>
       <c r="C268" s="7"/>
@@ -12643,7 +12643,7 @@
       <c r="AE268" s="7"/>
       <c r="AF268" s="7"/>
     </row>
-    <row r="269" spans="1:32">
+    <row r="269" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A269" s="7"/>
       <c r="B269" s="7"/>
       <c r="C269" s="7"/>
@@ -12677,7 +12677,7 @@
       <c r="AE269" s="7"/>
       <c r="AF269" s="7"/>
     </row>
-    <row r="270" spans="1:32">
+    <row r="270" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A270" s="7"/>
       <c r="B270" s="7"/>
       <c r="C270" s="7"/>
@@ -12711,7 +12711,7 @@
       <c r="AE270" s="7"/>
       <c r="AF270" s="7"/>
     </row>
-    <row r="271" spans="1:32">
+    <row r="271" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A271" s="7"/>
       <c r="B271" s="7"/>
       <c r="C271" s="7"/>
@@ -12745,7 +12745,7 @@
       <c r="AE271" s="7"/>
       <c r="AF271" s="7"/>
     </row>
-    <row r="272" spans="1:32">
+    <row r="272" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A272" s="7"/>
       <c r="B272" s="7"/>
       <c r="C272" s="7"/>
@@ -12779,7 +12779,7 @@
       <c r="AE272" s="7"/>
       <c r="AF272" s="7"/>
     </row>
-    <row r="273" spans="1:32">
+    <row r="273" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A273" s="7"/>
       <c r="B273" s="7"/>
       <c r="C273" s="7"/>
@@ -12813,7 +12813,7 @@
       <c r="AE273" s="7"/>
       <c r="AF273" s="7"/>
     </row>
-    <row r="274" spans="1:32">
+    <row r="274" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A274" s="7"/>
       <c r="B274" s="7"/>
       <c r="C274" s="7"/>
@@ -12847,7 +12847,7 @@
       <c r="AE274" s="7"/>
       <c r="AF274" s="7"/>
     </row>
-    <row r="275" spans="1:32">
+    <row r="275" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A275" s="7"/>
       <c r="B275" s="7"/>
       <c r="C275" s="7"/>
@@ -12881,7 +12881,7 @@
       <c r="AE275" s="7"/>
       <c r="AF275" s="7"/>
     </row>
-    <row r="276" spans="1:32">
+    <row r="276" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A276" s="7"/>
       <c r="B276" s="7"/>
       <c r="C276" s="7"/>
@@ -12915,7 +12915,7 @@
       <c r="AE276" s="7"/>
       <c r="AF276" s="7"/>
     </row>
-    <row r="277" spans="1:32">
+    <row r="277" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A277" s="7"/>
       <c r="B277" s="7"/>
       <c r="C277" s="7"/>
@@ -12949,7 +12949,7 @@
       <c r="AE277" s="7"/>
       <c r="AF277" s="7"/>
     </row>
-    <row r="278" spans="1:32">
+    <row r="278" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A278" s="7"/>
       <c r="B278" s="7"/>
       <c r="C278" s="7"/>
@@ -12983,7 +12983,7 @@
       <c r="AE278" s="7"/>
       <c r="AF278" s="7"/>
     </row>
-    <row r="279" spans="1:32">
+    <row r="279" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A279" s="7"/>
       <c r="B279" s="7"/>
       <c r="C279" s="7"/>
@@ -13017,7 +13017,7 @@
       <c r="AE279" s="7"/>
       <c r="AF279" s="7"/>
     </row>
-    <row r="280" spans="1:32">
+    <row r="280" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A280" s="7"/>
       <c r="B280" s="7"/>
       <c r="C280" s="7"/>
@@ -13051,7 +13051,7 @@
       <c r="AE280" s="7"/>
       <c r="AF280" s="7"/>
     </row>
-    <row r="281" spans="1:32">
+    <row r="281" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A281" s="7"/>
       <c r="B281" s="7"/>
       <c r="C281" s="7"/>
@@ -13085,7 +13085,7 @@
       <c r="AE281" s="7"/>
       <c r="AF281" s="7"/>
     </row>
-    <row r="282" spans="1:32">
+    <row r="282" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A282" s="7"/>
       <c r="B282" s="7"/>
       <c r="C282" s="7"/>
@@ -13119,7 +13119,7 @@
       <c r="AE282" s="7"/>
       <c r="AF282" s="7"/>
     </row>
-    <row r="283" spans="1:32">
+    <row r="283" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A283" s="7"/>
       <c r="B283" s="7"/>
       <c r="C283" s="7"/>
@@ -13153,7 +13153,7 @@
       <c r="AE283" s="7"/>
       <c r="AF283" s="7"/>
     </row>
-    <row r="284" spans="1:32">
+    <row r="284" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A284" s="7"/>
       <c r="B284" s="7"/>
       <c r="C284" s="7"/>
@@ -13187,7 +13187,7 @@
       <c r="AE284" s="7"/>
       <c r="AF284" s="7"/>
     </row>
-    <row r="285" spans="1:32">
+    <row r="285" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A285" s="7"/>
       <c r="B285" s="7"/>
       <c r="C285" s="7"/>
@@ -13221,7 +13221,7 @@
       <c r="AE285" s="7"/>
       <c r="AF285" s="7"/>
     </row>
-    <row r="286" spans="1:32">
+    <row r="286" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A286" s="7"/>
       <c r="B286" s="7"/>
       <c r="C286" s="7"/>
@@ -13255,7 +13255,7 @@
       <c r="AE286" s="7"/>
       <c r="AF286" s="7"/>
     </row>
-    <row r="287" spans="1:32">
+    <row r="287" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A287" s="7"/>
       <c r="B287" s="7"/>
       <c r="C287" s="7"/>
@@ -13289,7 +13289,7 @@
       <c r="AE287" s="7"/>
       <c r="AF287" s="7"/>
     </row>
-    <row r="288" spans="1:32">
+    <row r="288" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A288" s="7"/>
       <c r="B288" s="7"/>
       <c r="C288" s="7"/>
@@ -13323,7 +13323,7 @@
       <c r="AE288" s="7"/>
       <c r="AF288" s="7"/>
     </row>
-    <row r="289" spans="1:32">
+    <row r="289" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A289" s="7"/>
       <c r="B289" s="7"/>
       <c r="C289" s="7"/>
@@ -13357,7 +13357,7 @@
       <c r="AE289" s="7"/>
       <c r="AF289" s="7"/>
     </row>
-    <row r="290" spans="1:32">
+    <row r="290" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A290" s="7"/>
       <c r="B290" s="7"/>
       <c r="C290" s="7"/>
@@ -13391,7 +13391,7 @@
       <c r="AE290" s="7"/>
       <c r="AF290" s="7"/>
     </row>
-    <row r="291" spans="1:32">
+    <row r="291" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A291" s="7"/>
       <c r="B291" s="7"/>
       <c r="C291" s="7"/>
@@ -13425,7 +13425,7 @@
       <c r="AE291" s="7"/>
       <c r="AF291" s="7"/>
     </row>
-    <row r="292" spans="1:32">
+    <row r="292" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A292" s="7"/>
       <c r="B292" s="7"/>
       <c r="C292" s="7"/>
@@ -13459,7 +13459,7 @@
       <c r="AE292" s="7"/>
       <c r="AF292" s="7"/>
     </row>
-    <row r="293" spans="1:32">
+    <row r="293" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A293" s="7"/>
       <c r="B293" s="7"/>
       <c r="C293" s="7"/>
@@ -13493,7 +13493,7 @@
       <c r="AE293" s="7"/>
       <c r="AF293" s="7"/>
     </row>
-    <row r="294" spans="1:32">
+    <row r="294" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A294" s="7"/>
       <c r="B294" s="7"/>
       <c r="C294" s="7"/>
@@ -13527,7 +13527,7 @@
       <c r="AE294" s="7"/>
       <c r="AF294" s="7"/>
     </row>
-    <row r="295" spans="1:32">
+    <row r="295" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A295" s="7"/>
       <c r="B295" s="7"/>
       <c r="C295" s="7"/>
@@ -13561,7 +13561,7 @@
       <c r="AE295" s="7"/>
       <c r="AF295" s="7"/>
     </row>
-    <row r="296" spans="1:32">
+    <row r="296" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A296" s="7"/>
       <c r="B296" s="7"/>
       <c r="C296" s="7"/>
@@ -13595,7 +13595,7 @@
       <c r="AE296" s="7"/>
       <c r="AF296" s="7"/>
     </row>
-    <row r="297" spans="1:32">
+    <row r="297" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A297" s="7"/>
       <c r="B297" s="7"/>
       <c r="C297" s="7"/>
@@ -14023,7 +14023,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AF233"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.140625" customWidth="1"/>
     <col min="2" max="2" width="29.28515625" customWidth="1"/>
@@ -14044,15 +14044,15 @@
     <col min="19" max="19" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15.75" thickBot="1">
+    <row r="1" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
+      <c r="G1" s="173"/>
+      <c r="H1" s="173"/>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
@@ -14078,26 +14078,26 @@
       <c r="AE1" s="7"/>
       <c r="AF1" s="7"/>
     </row>
-    <row r="2" spans="1:32" ht="15" customHeight="1">
+    <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="156" t="s">
+      <c r="G2" s="173"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
-      <c r="L2" s="157"/>
-      <c r="M2" s="157"/>
-      <c r="N2" s="157"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="157"/>
-      <c r="Q2" s="158"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="119"/>
+      <c r="M2" s="119"/>
+      <c r="N2" s="119"/>
+      <c r="O2" s="119"/>
+      <c r="P2" s="119"/>
+      <c r="Q2" s="120"/>
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
       <c r="T2" s="7"/>
@@ -14114,24 +14114,24 @@
       <c r="AE2" s="7"/>
       <c r="AF2" s="7"/>
     </row>
-    <row r="3" spans="1:32" ht="15" customHeight="1">
+    <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
-      <c r="G3" s="143"/>
-      <c r="H3" s="143"/>
-      <c r="I3" s="159"/>
-      <c r="J3" s="160"/>
-      <c r="K3" s="160"/>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160"/>
-      <c r="N3" s="160"/>
-      <c r="O3" s="160"/>
-      <c r="P3" s="160"/>
-      <c r="Q3" s="161"/>
+      <c r="G3" s="173"/>
+      <c r="H3" s="173"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="122"/>
+      <c r="M3" s="122"/>
+      <c r="N3" s="122"/>
+      <c r="O3" s="122"/>
+      <c r="P3" s="122"/>
+      <c r="Q3" s="123"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
@@ -14148,24 +14148,24 @@
       <c r="AE3" s="7"/>
       <c r="AF3" s="7"/>
     </row>
-    <row r="4" spans="1:32" ht="15" customHeight="1" thickBot="1">
+    <row r="4" spans="1:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="143"/>
-      <c r="I4" s="162"/>
-      <c r="J4" s="163"/>
-      <c r="K4" s="163"/>
-      <c r="L4" s="163"/>
-      <c r="M4" s="163"/>
-      <c r="N4" s="163"/>
-      <c r="O4" s="163"/>
-      <c r="P4" s="163"/>
-      <c r="Q4" s="164"/>
+      <c r="G4" s="173"/>
+      <c r="H4" s="173"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="125"/>
+      <c r="M4" s="125"/>
+      <c r="N4" s="125"/>
+      <c r="O4" s="125"/>
+      <c r="P4" s="125"/>
+      <c r="Q4" s="126"/>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
@@ -14182,26 +14182,26 @@
       <c r="AE4" s="7"/>
       <c r="AF4" s="7"/>
     </row>
-    <row r="5" spans="1:32" ht="24.75" customHeight="1">
+    <row r="5" spans="1:32" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="143"/>
-      <c r="H5" s="143"/>
-      <c r="I5" s="165" t="s">
+      <c r="G5" s="173"/>
+      <c r="H5" s="173"/>
+      <c r="I5" s="127" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="166"/>
-      <c r="K5" s="166"/>
-      <c r="L5" s="166"/>
-      <c r="M5" s="166"/>
-      <c r="N5" s="166"/>
-      <c r="O5" s="166"/>
-      <c r="P5" s="166"/>
-      <c r="Q5" s="167"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="128"/>
+      <c r="N5" s="128"/>
+      <c r="O5" s="128"/>
+      <c r="P5" s="128"/>
+      <c r="Q5" s="129"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
@@ -14218,15 +14218,15 @@
       <c r="AE5" s="7"/>
       <c r="AF5" s="7"/>
     </row>
-    <row r="6" spans="1:32" ht="15" customHeight="1">
+    <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="143"/>
-      <c r="H6" s="143"/>
+      <c r="G6" s="173"/>
+      <c r="H6" s="173"/>
       <c r="I6" s="50" t="s">
         <v>49</v>
       </c>
@@ -14236,14 +14236,14 @@
       <c r="K6" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="L6" s="135" t="s">
+      <c r="L6" s="170" t="s">
         <v>39</v>
       </c>
-      <c r="M6" s="136"/>
-      <c r="N6" s="136"/>
-      <c r="O6" s="136"/>
-      <c r="P6" s="136"/>
-      <c r="Q6" s="137"/>
+      <c r="M6" s="171"/>
+      <c r="N6" s="171"/>
+      <c r="O6" s="171"/>
+      <c r="P6" s="171"/>
+      <c r="Q6" s="172"/>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7"/>
@@ -14260,15 +14260,15 @@
       <c r="AE6" s="7"/>
       <c r="AF6" s="7"/>
     </row>
-    <row r="7" spans="1:32" ht="15" customHeight="1" thickBot="1">
+    <row r="7" spans="1:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
-      <c r="G7" s="143"/>
-      <c r="H7" s="143"/>
+      <c r="G7" s="173"/>
+      <c r="H7" s="173"/>
       <c r="I7" s="51" t="s">
         <v>20</v>
       </c>
@@ -14280,14 +14280,14 @@
         <f>J7/J7</f>
         <v>1</v>
       </c>
-      <c r="L7" s="118" t="s">
+      <c r="L7" s="164" t="s">
         <v>68</v>
       </c>
-      <c r="M7" s="119"/>
-      <c r="N7" s="119"/>
-      <c r="O7" s="119"/>
-      <c r="P7" s="119"/>
-      <c r="Q7" s="120"/>
+      <c r="M7" s="165"/>
+      <c r="N7" s="165"/>
+      <c r="O7" s="165"/>
+      <c r="P7" s="165"/>
+      <c r="Q7" s="166"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
@@ -14304,17 +14304,17 @@
       <c r="AE7" s="7"/>
       <c r="AF7" s="7"/>
     </row>
-    <row r="8" spans="1:32" ht="15" customHeight="1">
+    <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7"/>
-      <c r="B8" s="181" t="s">
+      <c r="B8" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="182"/>
-      <c r="D8" s="182"/>
-      <c r="E8" s="182"/>
-      <c r="F8" s="183"/>
-      <c r="G8" s="143"/>
-      <c r="H8" s="143"/>
+      <c r="C8" s="146"/>
+      <c r="D8" s="146"/>
+      <c r="E8" s="146"/>
+      <c r="F8" s="147"/>
+      <c r="G8" s="173"/>
+      <c r="H8" s="173"/>
       <c r="I8" s="52" t="s">
         <v>6</v>
       </c>
@@ -14326,14 +14326,14 @@
         <f>J8/J7</f>
         <v>0.99942848039583176</v>
       </c>
-      <c r="L8" s="118" t="s">
+      <c r="L8" s="164" t="s">
         <v>69</v>
       </c>
-      <c r="M8" s="119"/>
-      <c r="N8" s="119"/>
-      <c r="O8" s="119"/>
-      <c r="P8" s="119"/>
-      <c r="Q8" s="120"/>
+      <c r="M8" s="165"/>
+      <c r="N8" s="165"/>
+      <c r="O8" s="165"/>
+      <c r="P8" s="165"/>
+      <c r="Q8" s="166"/>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
       <c r="T8" s="7"/>
@@ -14350,15 +14350,15 @@
       <c r="AE8" s="7"/>
       <c r="AF8" s="7"/>
     </row>
-    <row r="9" spans="1:32" ht="15" customHeight="1">
+    <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="7"/>
-      <c r="B9" s="184"/>
-      <c r="C9" s="185"/>
-      <c r="D9" s="185"/>
-      <c r="E9" s="185"/>
-      <c r="F9" s="186"/>
-      <c r="G9" s="143"/>
-      <c r="H9" s="143"/>
+      <c r="B9" s="148"/>
+      <c r="C9" s="149"/>
+      <c r="D9" s="149"/>
+      <c r="E9" s="149"/>
+      <c r="F9" s="150"/>
+      <c r="G9" s="173"/>
+      <c r="H9" s="173"/>
       <c r="I9" s="51" t="s">
         <v>8</v>
       </c>
@@ -14370,14 +14370,14 @@
         <f>J9/J7</f>
         <v>5.199840067971113E-4</v>
       </c>
-      <c r="L9" s="118" t="s">
+      <c r="L9" s="164" t="s">
         <v>69</v>
       </c>
-      <c r="M9" s="119"/>
-      <c r="N9" s="119"/>
-      <c r="O9" s="119"/>
-      <c r="P9" s="119"/>
-      <c r="Q9" s="120"/>
+      <c r="M9" s="165"/>
+      <c r="N9" s="165"/>
+      <c r="O9" s="165"/>
+      <c r="P9" s="165"/>
+      <c r="Q9" s="166"/>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
@@ -14394,15 +14394,15 @@
       <c r="AE9" s="7"/>
       <c r="AF9" s="7"/>
     </row>
-    <row r="10" spans="1:32" ht="15" customHeight="1" thickBot="1">
+    <row r="10" spans="1:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="7"/>
-      <c r="B10" s="187"/>
-      <c r="C10" s="188"/>
-      <c r="D10" s="188"/>
-      <c r="E10" s="188"/>
-      <c r="F10" s="189"/>
-      <c r="G10" s="143"/>
-      <c r="H10" s="143"/>
+      <c r="B10" s="151"/>
+      <c r="C10" s="152"/>
+      <c r="D10" s="152"/>
+      <c r="E10" s="152"/>
+      <c r="F10" s="153"/>
+      <c r="G10" s="173"/>
+      <c r="H10" s="173"/>
       <c r="I10" s="52" t="s">
         <v>9</v>
       </c>
@@ -14414,14 +14414,14 @@
         <f>J10/J7</f>
         <v>5.1535597371117274E-5</v>
       </c>
-      <c r="L10" s="118" t="s">
+      <c r="L10" s="164" t="s">
         <v>69</v>
       </c>
-      <c r="M10" s="119"/>
-      <c r="N10" s="119"/>
-      <c r="O10" s="119"/>
-      <c r="P10" s="119"/>
-      <c r="Q10" s="120"/>
+      <c r="M10" s="165"/>
+      <c r="N10" s="165"/>
+      <c r="O10" s="165"/>
+      <c r="P10" s="165"/>
+      <c r="Q10" s="166"/>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
@@ -14438,26 +14438,26 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="7"/>
     </row>
-    <row r="11" spans="1:32" ht="15" customHeight="1">
+    <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="7"/>
-      <c r="B11" s="146" t="s">
+      <c r="B11" s="154" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="147"/>
-      <c r="D11" s="147"/>
-      <c r="E11" s="147"/>
-      <c r="F11" s="148"/>
-      <c r="G11" s="143"/>
-      <c r="H11" s="143"/>
-      <c r="I11" s="134"/>
-      <c r="J11" s="134"/>
-      <c r="K11" s="134"/>
-      <c r="L11" s="134"/>
-      <c r="M11" s="134"/>
-      <c r="N11" s="134"/>
-      <c r="O11" s="134"/>
-      <c r="P11" s="134"/>
-      <c r="Q11" s="134"/>
+      <c r="C11" s="155"/>
+      <c r="D11" s="155"/>
+      <c r="E11" s="155"/>
+      <c r="F11" s="156"/>
+      <c r="G11" s="173"/>
+      <c r="H11" s="173"/>
+      <c r="I11" s="189"/>
+      <c r="J11" s="189"/>
+      <c r="K11" s="189"/>
+      <c r="L11" s="189"/>
+      <c r="M11" s="189"/>
+      <c r="N11" s="189"/>
+      <c r="O11" s="189"/>
+      <c r="P11" s="189"/>
+      <c r="Q11" s="189"/>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
@@ -14474,15 +14474,15 @@
       <c r="AE11" s="7"/>
       <c r="AF11" s="7"/>
     </row>
-    <row r="12" spans="1:32" ht="15" customHeight="1">
+    <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="7"/>
-      <c r="B12" s="149"/>
-      <c r="C12" s="150"/>
-      <c r="D12" s="150"/>
-      <c r="E12" s="150"/>
-      <c r="F12" s="151"/>
-      <c r="G12" s="143"/>
-      <c r="H12" s="143"/>
+      <c r="B12" s="157"/>
+      <c r="C12" s="158"/>
+      <c r="D12" s="158"/>
+      <c r="E12" s="158"/>
+      <c r="F12" s="159"/>
+      <c r="G12" s="173"/>
+      <c r="H12" s="173"/>
       <c r="I12" s="50" t="s">
         <v>51</v>
       </c>
@@ -14492,14 +14492,14 @@
       <c r="K12" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="L12" s="135" t="s">
+      <c r="L12" s="170" t="s">
         <v>39</v>
       </c>
-      <c r="M12" s="136"/>
-      <c r="N12" s="136"/>
-      <c r="O12" s="136"/>
-      <c r="P12" s="136"/>
-      <c r="Q12" s="137"/>
+      <c r="M12" s="171"/>
+      <c r="N12" s="171"/>
+      <c r="O12" s="171"/>
+      <c r="P12" s="171"/>
+      <c r="Q12" s="172"/>
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
       <c r="T12" s="7"/>
@@ -14516,19 +14516,19 @@
       <c r="AE12" s="7"/>
       <c r="AF12" s="7"/>
     </row>
-    <row r="13" spans="1:32" ht="15" customHeight="1">
+    <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="8"/>
-      <c r="B13" s="138" t="s">
+      <c r="B13" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="139"/>
-      <c r="D13" s="171" t="s">
+      <c r="C13" s="144"/>
+      <c r="D13" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="171"/>
-      <c r="F13" s="171"/>
-      <c r="G13" s="143"/>
-      <c r="H13" s="143"/>
+      <c r="E13" s="133"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="173"/>
+      <c r="H13" s="173"/>
       <c r="I13" s="51" t="s">
         <v>5</v>
       </c>
@@ -14540,14 +14540,14 @@
         <f>J13/J13</f>
         <v>1</v>
       </c>
-      <c r="L13" s="118" t="s">
+      <c r="L13" s="164" t="s">
         <v>71</v>
       </c>
-      <c r="M13" s="119"/>
-      <c r="N13" s="119"/>
-      <c r="O13" s="119"/>
-      <c r="P13" s="119"/>
-      <c r="Q13" s="120"/>
+      <c r="M13" s="165"/>
+      <c r="N13" s="165"/>
+      <c r="O13" s="165"/>
+      <c r="P13" s="165"/>
+      <c r="Q13" s="166"/>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
       <c r="T13" s="7"/>
@@ -14564,7 +14564,7 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="7"/>
     </row>
-    <row r="14" spans="1:32" ht="15" customHeight="1">
+    <row r="14" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="7"/>
       <c r="B14" s="4" t="s">
         <v>33</v>
@@ -14572,13 +14572,13 @@
       <c r="C14" s="44">
         <v>2000</v>
       </c>
-      <c r="D14" s="172" t="s">
+      <c r="D14" s="134" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="172"/>
-      <c r="F14" s="172"/>
-      <c r="G14" s="143"/>
-      <c r="H14" s="143"/>
+      <c r="E14" s="134"/>
+      <c r="F14" s="134"/>
+      <c r="G14" s="173"/>
+      <c r="H14" s="173"/>
       <c r="I14" s="52" t="s">
         <v>43</v>
       </c>
@@ -14590,14 +14590,14 @@
         <f>J14/J13</f>
         <v>0.99948199999999998</v>
       </c>
-      <c r="L14" s="140" t="s">
+      <c r="L14" s="167" t="s">
         <v>70</v>
       </c>
-      <c r="M14" s="141"/>
-      <c r="N14" s="141"/>
-      <c r="O14" s="141"/>
-      <c r="P14" s="141"/>
-      <c r="Q14" s="142"/>
+      <c r="M14" s="168"/>
+      <c r="N14" s="168"/>
+      <c r="O14" s="168"/>
+      <c r="P14" s="168"/>
+      <c r="Q14" s="169"/>
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
       <c r="T14" s="7"/>
@@ -14614,7 +14614,7 @@
       <c r="AE14" s="7"/>
       <c r="AF14" s="7"/>
     </row>
-    <row r="15" spans="1:32" ht="15" customHeight="1">
+    <row r="15" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="7"/>
       <c r="B15" s="5" t="s">
         <v>14</v>
@@ -14622,13 +14622,13 @@
       <c r="C15" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="173" t="s">
+      <c r="D15" s="135" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="173"/>
-      <c r="F15" s="173"/>
-      <c r="G15" s="143"/>
-      <c r="H15" s="143"/>
+      <c r="E15" s="135"/>
+      <c r="F15" s="135"/>
+      <c r="G15" s="173"/>
+      <c r="H15" s="173"/>
       <c r="I15" s="51" t="s">
         <v>44</v>
       </c>
@@ -14640,14 +14640,14 @@
         <f>J15/J13</f>
         <v>4.7999999999999996E-4</v>
       </c>
-      <c r="L15" s="118" t="s">
+      <c r="L15" s="164" t="s">
         <v>69</v>
       </c>
-      <c r="M15" s="119"/>
-      <c r="N15" s="119"/>
-      <c r="O15" s="119"/>
-      <c r="P15" s="119"/>
-      <c r="Q15" s="120"/>
+      <c r="M15" s="165"/>
+      <c r="N15" s="165"/>
+      <c r="O15" s="165"/>
+      <c r="P15" s="165"/>
+      <c r="Q15" s="166"/>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
       <c r="T15" s="7"/>
@@ -14664,7 +14664,7 @@
       <c r="AE15" s="7"/>
       <c r="AF15" s="7"/>
     </row>
-    <row r="16" spans="1:32" ht="15" customHeight="1">
+    <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="7"/>
       <c r="B16" s="4" t="s">
         <v>34</v>
@@ -14672,13 +14672,13 @@
       <c r="C16" s="45">
         <v>0.98</v>
       </c>
-      <c r="D16" s="174" t="s">
+      <c r="D16" s="136" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="175"/>
-      <c r="F16" s="176"/>
-      <c r="G16" s="143"/>
-      <c r="H16" s="143"/>
+      <c r="E16" s="137"/>
+      <c r="F16" s="138"/>
+      <c r="G16" s="173"/>
+      <c r="H16" s="173"/>
       <c r="I16" s="52" t="s">
         <v>45</v>
       </c>
@@ -14690,14 +14690,14 @@
         <f>J16/J13</f>
         <v>3.8000000000000002E-5</v>
       </c>
-      <c r="L16" s="118" t="s">
+      <c r="L16" s="164" t="s">
         <v>69</v>
       </c>
-      <c r="M16" s="119"/>
-      <c r="N16" s="119"/>
-      <c r="O16" s="119"/>
-      <c r="P16" s="119"/>
-      <c r="Q16" s="120"/>
+      <c r="M16" s="165"/>
+      <c r="N16" s="165"/>
+      <c r="O16" s="165"/>
+      <c r="P16" s="165"/>
+      <c r="Q16" s="166"/>
       <c r="R16" s="7"/>
       <c r="S16" s="7"/>
       <c r="T16" s="7"/>
@@ -14714,7 +14714,7 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="7"/>
     </row>
-    <row r="17" spans="1:32" ht="15" customHeight="1">
+    <row r="17" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="7"/>
       <c r="B17" s="5" t="s">
         <v>15</v>
@@ -14722,22 +14722,22 @@
       <c r="C17" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="177" t="s">
+      <c r="D17" s="139" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="178"/>
-      <c r="F17" s="179"/>
-      <c r="G17" s="143"/>
-      <c r="H17" s="143"/>
-      <c r="I17" s="140"/>
-      <c r="J17" s="141"/>
-      <c r="K17" s="141"/>
-      <c r="L17" s="141"/>
-      <c r="M17" s="141"/>
-      <c r="N17" s="141"/>
-      <c r="O17" s="141"/>
-      <c r="P17" s="141"/>
-      <c r="Q17" s="142"/>
+      <c r="E17" s="140"/>
+      <c r="F17" s="141"/>
+      <c r="G17" s="173"/>
+      <c r="H17" s="173"/>
+      <c r="I17" s="167"/>
+      <c r="J17" s="168"/>
+      <c r="K17" s="168"/>
+      <c r="L17" s="168"/>
+      <c r="M17" s="168"/>
+      <c r="N17" s="168"/>
+      <c r="O17" s="168"/>
+      <c r="P17" s="168"/>
+      <c r="Q17" s="169"/>
       <c r="R17" s="7"/>
       <c r="S17" s="7"/>
       <c r="T17" s="7"/>
@@ -14754,7 +14754,7 @@
       <c r="AE17" s="7"/>
       <c r="AF17" s="7"/>
     </row>
-    <row r="18" spans="1:32" ht="15" customHeight="1">
+    <row r="18" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="7"/>
       <c r="B18" s="4" t="s">
         <v>35</v>
@@ -14762,13 +14762,13 @@
       <c r="C18" s="45">
         <v>0.02</v>
       </c>
-      <c r="D18" s="174" t="s">
+      <c r="D18" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="175"/>
-      <c r="F18" s="176"/>
-      <c r="G18" s="143"/>
-      <c r="H18" s="143"/>
+      <c r="E18" s="137"/>
+      <c r="F18" s="138"/>
+      <c r="G18" s="173"/>
+      <c r="H18" s="173"/>
       <c r="I18" s="50" t="s">
         <v>29</v>
       </c>
@@ -14778,14 +14778,14 @@
       <c r="K18" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="L18" s="135" t="s">
+      <c r="L18" s="170" t="s">
         <v>39</v>
       </c>
-      <c r="M18" s="136"/>
-      <c r="N18" s="136"/>
-      <c r="O18" s="136"/>
-      <c r="P18" s="136"/>
-      <c r="Q18" s="137"/>
+      <c r="M18" s="171"/>
+      <c r="N18" s="171"/>
+      <c r="O18" s="171"/>
+      <c r="P18" s="171"/>
+      <c r="Q18" s="172"/>
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
       <c r="T18" s="7"/>
@@ -14802,15 +14802,15 @@
       <c r="AE18" s="7"/>
       <c r="AF18" s="7"/>
     </row>
-    <row r="19" spans="1:32" ht="15" customHeight="1">
+    <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="7"/>
-      <c r="B19" s="173"/>
-      <c r="C19" s="173"/>
-      <c r="D19" s="173"/>
-      <c r="E19" s="173"/>
-      <c r="F19" s="173"/>
-      <c r="G19" s="143"/>
-      <c r="H19" s="143"/>
+      <c r="B19" s="135"/>
+      <c r="C19" s="135"/>
+      <c r="D19" s="135"/>
+      <c r="E19" s="135"/>
+      <c r="F19" s="135"/>
+      <c r="G19" s="173"/>
+      <c r="H19" s="173"/>
       <c r="I19" s="51" t="s">
         <v>5</v>
       </c>
@@ -14822,14 +14822,14 @@
         <f>J19/J19</f>
         <v>1</v>
       </c>
-      <c r="L19" s="118" t="s">
+      <c r="L19" s="164" t="s">
         <v>55</v>
       </c>
-      <c r="M19" s="119"/>
-      <c r="N19" s="119"/>
-      <c r="O19" s="119"/>
-      <c r="P19" s="119"/>
-      <c r="Q19" s="120"/>
+      <c r="M19" s="165"/>
+      <c r="N19" s="165"/>
+      <c r="O19" s="165"/>
+      <c r="P19" s="165"/>
+      <c r="Q19" s="166"/>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
       <c r="T19" s="7"/>
@@ -14846,19 +14846,19 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="7"/>
     </row>
-    <row r="20" spans="1:32" ht="15" customHeight="1">
+    <row r="20" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="7"/>
-      <c r="B20" s="138" t="s">
+      <c r="B20" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="139"/>
-      <c r="D20" s="171" t="s">
+      <c r="C20" s="144"/>
+      <c r="D20" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="171"/>
-      <c r="F20" s="171"/>
-      <c r="G20" s="143"/>
-      <c r="H20" s="143"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="133"/>
+      <c r="G20" s="173"/>
+      <c r="H20" s="173"/>
       <c r="I20" s="52" t="s">
         <v>43</v>
       </c>
@@ -14870,14 +14870,14 @@
         <f>J20/J19</f>
         <v>0.87350000000000005</v>
       </c>
-      <c r="L20" s="118" t="s">
+      <c r="L20" s="164" t="s">
         <v>69</v>
       </c>
-      <c r="M20" s="119"/>
-      <c r="N20" s="119"/>
-      <c r="O20" s="119"/>
-      <c r="P20" s="119"/>
-      <c r="Q20" s="120"/>
+      <c r="M20" s="165"/>
+      <c r="N20" s="165"/>
+      <c r="O20" s="165"/>
+      <c r="P20" s="165"/>
+      <c r="Q20" s="166"/>
       <c r="R20" s="7"/>
       <c r="S20" s="7"/>
       <c r="T20" s="7"/>
@@ -14894,7 +14894,7 @@
       <c r="AE20" s="7"/>
       <c r="AF20" s="7"/>
     </row>
-    <row r="21" spans="1:32" ht="15" customHeight="1">
+    <row r="21" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="7"/>
       <c r="B21" s="4" t="s">
         <v>10</v>
@@ -14902,13 +14902,13 @@
       <c r="C21" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="177" t="s">
+      <c r="D21" s="139" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="178"/>
-      <c r="F21" s="179"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="143"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="141"/>
+      <c r="G21" s="173"/>
+      <c r="H21" s="173"/>
       <c r="I21" s="51" t="s">
         <v>44</v>
       </c>
@@ -14920,14 +14920,14 @@
         <f>J21/J19</f>
         <v>9.4600000000000004E-2</v>
       </c>
-      <c r="L21" s="118" t="s">
+      <c r="L21" s="164" t="s">
         <v>69</v>
       </c>
-      <c r="M21" s="119"/>
-      <c r="N21" s="119"/>
-      <c r="O21" s="119"/>
-      <c r="P21" s="119"/>
-      <c r="Q21" s="120"/>
+      <c r="M21" s="165"/>
+      <c r="N21" s="165"/>
+      <c r="O21" s="165"/>
+      <c r="P21" s="165"/>
+      <c r="Q21" s="166"/>
       <c r="R21" s="7"/>
       <c r="S21" s="7"/>
       <c r="T21" s="7"/>
@@ -14944,7 +14944,7 @@
       <c r="AE21" s="7"/>
       <c r="AF21" s="7"/>
     </row>
-    <row r="22" spans="1:32" ht="15" customHeight="1" thickBot="1">
+    <row r="22" spans="1:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A22" s="7"/>
       <c r="B22" s="6" t="s">
         <v>18</v>
@@ -14952,13 +14952,13 @@
       <c r="C22" s="46">
         <v>250000</v>
       </c>
-      <c r="D22" s="180" t="s">
+      <c r="D22" s="142" t="s">
         <v>67</v>
       </c>
-      <c r="E22" s="180"/>
-      <c r="F22" s="180"/>
-      <c r="G22" s="143"/>
-      <c r="H22" s="143"/>
+      <c r="E22" s="142"/>
+      <c r="F22" s="142"/>
+      <c r="G22" s="173"/>
+      <c r="H22" s="173"/>
       <c r="I22" s="53" t="s">
         <v>45</v>
       </c>
@@ -14970,14 +14970,14 @@
         <f>J22/J19</f>
         <v>3.1899999999999998E-2</v>
       </c>
-      <c r="L22" s="118" t="s">
+      <c r="L22" s="164" t="s">
         <v>69</v>
       </c>
-      <c r="M22" s="119"/>
-      <c r="N22" s="119"/>
-      <c r="O22" s="119"/>
-      <c r="P22" s="119"/>
-      <c r="Q22" s="120"/>
+      <c r="M22" s="165"/>
+      <c r="N22" s="165"/>
+      <c r="O22" s="165"/>
+      <c r="P22" s="165"/>
+      <c r="Q22" s="166"/>
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
@@ -14994,24 +14994,24 @@
       <c r="AE22" s="7"/>
       <c r="AF22" s="7"/>
     </row>
-    <row r="23" spans="1:32" ht="15.75" customHeight="1" thickBot="1">
+    <row r="23" spans="1:32" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="7"/>
-      <c r="B23" s="168"/>
-      <c r="C23" s="169"/>
-      <c r="D23" s="169"/>
-      <c r="E23" s="169"/>
-      <c r="F23" s="170"/>
-      <c r="G23" s="143"/>
-      <c r="H23" s="143"/>
-      <c r="I23" s="129"/>
-      <c r="J23" s="130"/>
-      <c r="K23" s="130"/>
-      <c r="L23" s="130"/>
-      <c r="M23" s="130"/>
-      <c r="N23" s="130"/>
-      <c r="O23" s="130"/>
-      <c r="P23" s="130"/>
-      <c r="Q23" s="131"/>
+      <c r="B23" s="130"/>
+      <c r="C23" s="131"/>
+      <c r="D23" s="131"/>
+      <c r="E23" s="131"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="173"/>
+      <c r="H23" s="173"/>
+      <c r="I23" s="184"/>
+      <c r="J23" s="185"/>
+      <c r="K23" s="185"/>
+      <c r="L23" s="185"/>
+      <c r="M23" s="185"/>
+      <c r="N23" s="185"/>
+      <c r="O23" s="185"/>
+      <c r="P23" s="185"/>
+      <c r="Q23" s="186"/>
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
@@ -15028,28 +15028,28 @@
       <c r="AE23" s="7"/>
       <c r="AF23" s="7"/>
     </row>
-    <row r="24" spans="1:32" ht="15" customHeight="1">
+    <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="7"/>
-      <c r="B24" s="146" t="s">
+      <c r="B24" s="154" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="147"/>
-      <c r="D24" s="147"/>
-      <c r="E24" s="147"/>
-      <c r="F24" s="148"/>
-      <c r="G24" s="143"/>
-      <c r="H24" s="143"/>
-      <c r="I24" s="123" t="s">
+      <c r="C24" s="155"/>
+      <c r="D24" s="155"/>
+      <c r="E24" s="155"/>
+      <c r="F24" s="156"/>
+      <c r="G24" s="173"/>
+      <c r="H24" s="173"/>
+      <c r="I24" s="178" t="s">
         <v>42</v>
       </c>
-      <c r="J24" s="124"/>
-      <c r="K24" s="124"/>
-      <c r="L24" s="124"/>
-      <c r="M24" s="124"/>
-      <c r="N24" s="124"/>
-      <c r="O24" s="124"/>
-      <c r="P24" s="124"/>
-      <c r="Q24" s="125"/>
+      <c r="J24" s="179"/>
+      <c r="K24" s="179"/>
+      <c r="L24" s="179"/>
+      <c r="M24" s="179"/>
+      <c r="N24" s="179"/>
+      <c r="O24" s="179"/>
+      <c r="P24" s="179"/>
+      <c r="Q24" s="180"/>
       <c r="R24" s="7"/>
       <c r="S24" s="7"/>
       <c r="T24" s="7"/>
@@ -15066,24 +15066,24 @@
       <c r="AE24" s="7"/>
       <c r="AF24" s="7"/>
     </row>
-    <row r="25" spans="1:32" ht="15" customHeight="1">
+    <row r="25" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="7"/>
-      <c r="B25" s="149"/>
-      <c r="C25" s="150"/>
-      <c r="D25" s="150"/>
-      <c r="E25" s="150"/>
-      <c r="F25" s="151"/>
-      <c r="G25" s="143"/>
-      <c r="H25" s="143"/>
-      <c r="I25" s="126"/>
-      <c r="J25" s="127"/>
-      <c r="K25" s="127"/>
-      <c r="L25" s="127"/>
-      <c r="M25" s="127"/>
-      <c r="N25" s="127"/>
-      <c r="O25" s="127"/>
-      <c r="P25" s="127"/>
-      <c r="Q25" s="128"/>
+      <c r="B25" s="157"/>
+      <c r="C25" s="158"/>
+      <c r="D25" s="158"/>
+      <c r="E25" s="158"/>
+      <c r="F25" s="159"/>
+      <c r="G25" s="173"/>
+      <c r="H25" s="173"/>
+      <c r="I25" s="181"/>
+      <c r="J25" s="182"/>
+      <c r="K25" s="182"/>
+      <c r="L25" s="182"/>
+      <c r="M25" s="182"/>
+      <c r="N25" s="182"/>
+      <c r="O25" s="182"/>
+      <c r="P25" s="182"/>
+      <c r="Q25" s="183"/>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
@@ -15100,50 +15100,50 @@
       <c r="AE25" s="7"/>
       <c r="AF25" s="7"/>
     </row>
-    <row r="26" spans="1:32" ht="19.5" customHeight="1">
+    <row r="26" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="7"/>
-      <c r="B26" s="144" t="s">
+      <c r="B26" s="176" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="144" t="s">
+      <c r="C26" s="176" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="152" t="s">
+      <c r="D26" s="160" t="s">
         <v>47</v>
       </c>
-      <c r="E26" s="152" t="s">
+      <c r="E26" s="160" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="154" t="s">
+      <c r="F26" s="162" t="s">
         <v>66</v>
       </c>
-      <c r="G26" s="143"/>
-      <c r="H26" s="143"/>
-      <c r="I26" s="132" t="s">
+      <c r="G26" s="173"/>
+      <c r="H26" s="173"/>
+      <c r="I26" s="187" t="s">
         <v>53</v>
       </c>
-      <c r="J26" s="132" t="s">
+      <c r="J26" s="187" t="s">
         <v>54</v>
       </c>
-      <c r="K26" s="121" t="s">
+      <c r="K26" s="174" t="s">
         <v>74</v>
       </c>
-      <c r="L26" s="121" t="s">
+      <c r="L26" s="174" t="s">
         <v>52</v>
       </c>
-      <c r="M26" s="121" t="s">
+      <c r="M26" s="174" t="s">
         <v>59</v>
       </c>
-      <c r="N26" s="121" t="s">
+      <c r="N26" s="174" t="s">
         <v>62</v>
       </c>
-      <c r="O26" s="121" t="s">
+      <c r="O26" s="174" t="s">
         <v>73</v>
       </c>
-      <c r="P26" s="121" t="s">
+      <c r="P26" s="174" t="s">
         <v>64</v>
       </c>
-      <c r="Q26" s="121" t="s">
+      <c r="Q26" s="174" t="s">
         <v>65</v>
       </c>
       <c r="R26" s="9"/>
@@ -15162,24 +15162,24 @@
       <c r="AE26" s="7"/>
       <c r="AF26" s="7"/>
     </row>
-    <row r="27" spans="1:32" ht="19.5" customHeight="1">
+    <row r="27" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="7"/>
-      <c r="B27" s="145"/>
-      <c r="C27" s="145"/>
-      <c r="D27" s="153"/>
-      <c r="E27" s="153"/>
-      <c r="F27" s="155"/>
-      <c r="G27" s="143"/>
-      <c r="H27" s="143"/>
-      <c r="I27" s="133"/>
-      <c r="J27" s="133"/>
-      <c r="K27" s="122"/>
-      <c r="L27" s="122"/>
-      <c r="M27" s="122"/>
-      <c r="N27" s="122"/>
-      <c r="O27" s="122"/>
-      <c r="P27" s="122"/>
-      <c r="Q27" s="122"/>
+      <c r="B27" s="177"/>
+      <c r="C27" s="177"/>
+      <c r="D27" s="161"/>
+      <c r="E27" s="161"/>
+      <c r="F27" s="163"/>
+      <c r="G27" s="173"/>
+      <c r="H27" s="173"/>
+      <c r="I27" s="188"/>
+      <c r="J27" s="188"/>
+      <c r="K27" s="175"/>
+      <c r="L27" s="175"/>
+      <c r="M27" s="175"/>
+      <c r="N27" s="175"/>
+      <c r="O27" s="175"/>
+      <c r="P27" s="175"/>
+      <c r="Q27" s="175"/>
       <c r="R27" s="7" t="s">
         <v>84</v>
       </c>
@@ -15200,56 +15200,56 @@
       <c r="AE27" s="7"/>
       <c r="AF27" s="7"/>
     </row>
-    <row r="28" spans="1:32">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A28" s="93"/>
       <c r="B28" s="47"/>
       <c r="C28" s="47"/>
       <c r="D28" s="48">
-        <v>4.1575040000000012</v>
+        <v>2.8380318246143235</v>
       </c>
       <c r="E28" s="48">
-        <v>5.2456879999999995</v>
+        <v>3.5597354124795313</v>
       </c>
       <c r="F28" s="103">
         <v>1.5E-6</v>
       </c>
-      <c r="G28" s="143"/>
-      <c r="H28" s="143"/>
+      <c r="G28" s="173"/>
+      <c r="H28" s="173"/>
       <c r="I28" s="99">
         <f t="shared" ref="I28:I47" si="1">IF(D28=0,"",LOG($K$15*10^D28+$K$16*10^E28+$K$14))</f>
-        <v>1.1640116161103842</v>
+        <v>0.16670977104284682</v>
       </c>
       <c r="J28" s="99">
         <f t="shared" ref="J28:J47" si="2">IF(D28=0,"",LOG($K$21*10^D28+$K$22*10^E28+$K$20))</f>
-        <v>3.8436743524136028</v>
+        <v>2.259536875659184</v>
       </c>
       <c r="K28" s="100">
         <f t="shared" ref="K28:K47" si="3">IF(D28=0,"",1/(1+10^D28*$J$15/$J$14+10^E28*$J$16/$J$14+10^J28*$J$19/$J$14))</f>
-        <v>5.6938225022651778E-2</v>
+        <v>0.64683026107510377</v>
       </c>
       <c r="L28" s="100">
         <f t="shared" ref="L28:L47" si="4">IF(D28=0,"",1/(1+10^I28/10^J28*$J$13/$J$19))</f>
-        <v>0.16892433959212033</v>
+        <v>4.9996679067413508E-2</v>
       </c>
       <c r="M28" s="100">
         <f t="shared" ref="M28:M47" si="5">IF(D28=0,"",1-L28)</f>
-        <v>0.83107566040787972</v>
+        <v>0.95000332093258644</v>
       </c>
       <c r="N28" s="100">
         <f t="shared" ref="N28:N47" si="6">IF(D28=0,"",1/(1/10^E28*$J$20/$J$22+10^D28/10^E28*$J$21/$J$22+10^I28/10^E28*$J$13/$J$22+1))</f>
-        <v>0.13598673930502334</v>
+        <v>3.1836871021025615E-2</v>
       </c>
       <c r="O28" s="41">
         <f t="shared" ref="O28:O47" si="7">IF(D28=0,"",F28*K28*$J$7/$J$14)</f>
-        <v>8.548791839415778E-8</v>
+        <v>9.7116080720222185E-7</v>
       </c>
       <c r="P28" s="41">
         <f t="shared" ref="P28:P47" si="8">IF(D28=0,"",O28*10^J28)</f>
-        <v>5.964569380109895E-4</v>
+        <v>1.7653386231535471E-4</v>
       </c>
       <c r="Q28" s="41">
         <f t="shared" ref="Q28:Q47" si="9">IF(D28=0,"",F28*N28*$J$7/$J$22)</f>
-        <v>1.5051949142824412E-2</v>
+        <v>3.5239242144063676E-3</v>
       </c>
       <c r="R28" s="9">
         <f>F28*0.002*1000000</f>
@@ -15257,9 +15257,12 @@
       </c>
       <c r="S28" s="11">
         <f>R28*L28</f>
-        <v>5.0677301877636097E-4</v>
-      </c>
-      <c r="T28" s="9"/>
+        <v>1.4999003720224052E-4</v>
+      </c>
+      <c r="T28" s="9">
+        <f>R28*M28</f>
+        <v>2.8500099627977592E-3</v>
+      </c>
       <c r="U28" s="7"/>
       <c r="V28" s="7"/>
       <c r="W28" s="7"/>
@@ -15273,56 +15276,56 @@
       <c r="AE28" s="7"/>
       <c r="AF28" s="7"/>
     </row>
-    <row r="29" spans="1:32">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A29" s="93"/>
       <c r="B29" s="47"/>
       <c r="C29" s="47"/>
       <c r="D29" s="48">
-        <v>4.1575040000000012</v>
+        <v>2.8380318246143235</v>
       </c>
       <c r="E29" s="48">
-        <v>5.2456879999999995</v>
+        <v>3.5597354124795313</v>
       </c>
       <c r="F29" s="103">
         <v>1.5E-5</v>
       </c>
-      <c r="G29" s="143"/>
-      <c r="H29" s="143"/>
+      <c r="G29" s="173"/>
+      <c r="H29" s="173"/>
       <c r="I29" s="99">
         <f t="shared" si="1"/>
-        <v>1.1640116161103842</v>
+        <v>0.16670977104284682</v>
       </c>
       <c r="J29" s="99">
         <f t="shared" si="2"/>
-        <v>3.8436743524136028</v>
+        <v>2.259536875659184</v>
       </c>
       <c r="K29" s="100">
         <f t="shared" si="3"/>
-        <v>5.6938225022651778E-2</v>
+        <v>0.64683026107510377</v>
       </c>
       <c r="L29" s="100">
         <f t="shared" si="4"/>
-        <v>0.16892433959212033</v>
+        <v>4.9996679067413508E-2</v>
       </c>
       <c r="M29" s="100">
         <f t="shared" si="5"/>
-        <v>0.83107566040787972</v>
+        <v>0.95000332093258644</v>
       </c>
       <c r="N29" s="100">
         <f t="shared" si="6"/>
-        <v>0.13598673930502334</v>
+        <v>3.1836871021025615E-2</v>
       </c>
       <c r="O29" s="41">
         <f t="shared" si="7"/>
-        <v>8.5487918394157786E-7</v>
+        <v>9.7116080720222176E-6</v>
       </c>
       <c r="P29" s="41">
         <f t="shared" si="8"/>
-        <v>5.9645693801098952E-3</v>
+        <v>1.765338623153547E-3</v>
       </c>
       <c r="Q29" s="41">
         <f t="shared" si="9"/>
-        <v>0.15051949142824411</v>
+        <v>3.5239242144063675E-2</v>
       </c>
       <c r="R29" s="9">
         <f>F29*0.002*1000000</f>
@@ -15330,9 +15333,12 @@
       </c>
       <c r="S29" s="11">
         <f>R29*L29</f>
-        <v>5.0677301877636105E-3</v>
-      </c>
-      <c r="T29" s="9"/>
+        <v>1.4999003720224053E-3</v>
+      </c>
+      <c r="T29" s="9">
+        <f>R29*M29</f>
+        <v>2.8500099627977594E-2</v>
+      </c>
       <c r="U29" s="7"/>
       <c r="V29" s="7"/>
       <c r="W29" s="7"/>
@@ -15346,15 +15352,15 @@
       <c r="AE29" s="7"/>
       <c r="AF29" s="7"/>
     </row>
-    <row r="30" spans="1:32">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A30" s="94"/>
       <c r="B30" s="47"/>
       <c r="C30" s="47"/>
       <c r="D30" s="95"/>
       <c r="E30" s="95"/>
       <c r="F30" s="103"/>
-      <c r="G30" s="143"/>
-      <c r="H30" s="143"/>
+      <c r="G30" s="173"/>
+      <c r="H30" s="173"/>
       <c r="I30" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15407,15 +15413,15 @@
       <c r="AE30" s="7"/>
       <c r="AF30" s="7"/>
     </row>
-    <row r="31" spans="1:32">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A31" s="94"/>
       <c r="B31" s="47"/>
       <c r="C31" s="47"/>
       <c r="D31" s="48"/>
       <c r="E31" s="48"/>
       <c r="F31" s="98"/>
-      <c r="G31" s="143"/>
-      <c r="H31" s="143"/>
+      <c r="G31" s="173"/>
+      <c r="H31" s="173"/>
       <c r="I31" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15468,15 +15474,15 @@
       <c r="AE31" s="7"/>
       <c r="AF31" s="7"/>
     </row>
-    <row r="32" spans="1:32">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A32" s="94"/>
       <c r="B32" s="47"/>
       <c r="C32" s="47"/>
       <c r="D32" s="48"/>
       <c r="E32" s="48"/>
       <c r="F32" s="98"/>
-      <c r="G32" s="143"/>
-      <c r="H32" s="143"/>
+      <c r="G32" s="173"/>
+      <c r="H32" s="173"/>
       <c r="I32" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15529,15 +15535,15 @@
       <c r="AE32" s="7"/>
       <c r="AF32" s="7"/>
     </row>
-    <row r="33" spans="1:32">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A33" s="94"/>
       <c r="B33" s="101"/>
       <c r="C33" s="101"/>
       <c r="D33" s="102"/>
       <c r="E33" s="102"/>
       <c r="F33" s="98"/>
-      <c r="G33" s="143"/>
-      <c r="H33" s="143"/>
+      <c r="G33" s="173"/>
+      <c r="H33" s="173"/>
       <c r="I33" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15590,15 +15596,15 @@
       <c r="AE33" s="7"/>
       <c r="AF33" s="7"/>
     </row>
-    <row r="34" spans="1:32">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A34" s="93"/>
       <c r="B34" s="47"/>
       <c r="C34" s="47"/>
       <c r="D34" s="95"/>
       <c r="E34" s="95"/>
       <c r="F34" s="98"/>
-      <c r="G34" s="143"/>
-      <c r="H34" s="143"/>
+      <c r="G34" s="173"/>
+      <c r="H34" s="173"/>
       <c r="I34" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15651,15 +15657,15 @@
       <c r="AE34" s="7"/>
       <c r="AF34" s="7"/>
     </row>
-    <row r="35" spans="1:32">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A35" s="93"/>
       <c r="B35" s="47"/>
       <c r="C35" s="47"/>
       <c r="D35" s="95"/>
       <c r="E35" s="95"/>
       <c r="F35" s="96"/>
-      <c r="G35" s="143"/>
-      <c r="H35" s="143"/>
+      <c r="G35" s="173"/>
+      <c r="H35" s="173"/>
       <c r="I35" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15712,15 +15718,15 @@
       <c r="AE35" s="7"/>
       <c r="AF35" s="7"/>
     </row>
-    <row r="36" spans="1:32">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A36" s="93"/>
       <c r="B36" s="47"/>
       <c r="C36" s="47"/>
       <c r="D36" s="48"/>
       <c r="E36" s="48"/>
       <c r="F36" s="96"/>
-      <c r="G36" s="143"/>
-      <c r="H36" s="143"/>
+      <c r="G36" s="173"/>
+      <c r="H36" s="173"/>
       <c r="I36" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15773,15 +15779,15 @@
       <c r="AE36" s="7"/>
       <c r="AF36" s="7"/>
     </row>
-    <row r="37" spans="1:32">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A37" s="93"/>
       <c r="B37" s="101"/>
       <c r="C37" s="101"/>
       <c r="D37" s="102"/>
       <c r="E37" s="102"/>
       <c r="F37" s="96"/>
-      <c r="G37" s="143"/>
-      <c r="H37" s="143"/>
+      <c r="G37" s="173"/>
+      <c r="H37" s="173"/>
       <c r="I37" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15834,15 +15840,15 @@
       <c r="AE37" s="7"/>
       <c r="AF37" s="7"/>
     </row>
-    <row r="38" spans="1:32">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A38" s="93"/>
       <c r="B38" s="47"/>
       <c r="C38" s="47"/>
       <c r="D38" s="95"/>
       <c r="E38" s="95"/>
       <c r="F38" s="96"/>
-      <c r="G38" s="143"/>
-      <c r="H38" s="143"/>
+      <c r="G38" s="173"/>
+      <c r="H38" s="173"/>
       <c r="I38" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15895,15 +15901,15 @@
       <c r="AE38" s="7"/>
       <c r="AF38" s="7"/>
     </row>
-    <row r="39" spans="1:32">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A39" s="93"/>
       <c r="B39" s="47"/>
       <c r="C39" s="47"/>
       <c r="D39" s="95"/>
       <c r="E39" s="95"/>
       <c r="F39" s="96"/>
-      <c r="G39" s="143"/>
-      <c r="H39" s="143"/>
+      <c r="G39" s="173"/>
+      <c r="H39" s="173"/>
       <c r="I39" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15956,15 +15962,15 @@
       <c r="AE39" s="7"/>
       <c r="AF39" s="7"/>
     </row>
-    <row r="40" spans="1:32">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A40" s="93"/>
       <c r="B40" s="47"/>
       <c r="C40" s="47"/>
       <c r="D40" s="48"/>
       <c r="E40" s="48"/>
       <c r="F40" s="96"/>
-      <c r="G40" s="143"/>
-      <c r="H40" s="143"/>
+      <c r="G40" s="173"/>
+      <c r="H40" s="173"/>
       <c r="I40" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16017,15 +16023,15 @@
       <c r="AE40" s="7"/>
       <c r="AF40" s="7"/>
     </row>
-    <row r="41" spans="1:32">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A41" s="93"/>
       <c r="B41" s="101"/>
       <c r="C41" s="101"/>
       <c r="D41" s="102"/>
       <c r="E41" s="102"/>
       <c r="F41" s="96"/>
-      <c r="G41" s="143"/>
-      <c r="H41" s="143"/>
+      <c r="G41" s="173"/>
+      <c r="H41" s="173"/>
       <c r="I41" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16078,15 +16084,15 @@
       <c r="AE41" s="7"/>
       <c r="AF41" s="7"/>
     </row>
-    <row r="42" spans="1:32">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A42" s="94"/>
       <c r="B42" s="47"/>
       <c r="C42" s="47"/>
       <c r="D42" s="95"/>
       <c r="E42" s="95"/>
       <c r="F42" s="96"/>
-      <c r="G42" s="143"/>
-      <c r="H42" s="143"/>
+      <c r="G42" s="173"/>
+      <c r="H42" s="173"/>
       <c r="I42" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16139,15 +16145,15 @@
       <c r="AE42" s="7"/>
       <c r="AF42" s="7"/>
     </row>
-    <row r="43" spans="1:32">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A43" s="94"/>
       <c r="B43" s="47"/>
       <c r="C43" s="47"/>
       <c r="D43" s="95"/>
       <c r="E43" s="95"/>
       <c r="F43" s="96"/>
-      <c r="G43" s="143"/>
-      <c r="H43" s="143"/>
+      <c r="G43" s="173"/>
+      <c r="H43" s="173"/>
       <c r="I43" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16200,15 +16206,15 @@
       <c r="AE43" s="7"/>
       <c r="AF43" s="7"/>
     </row>
-    <row r="44" spans="1:32">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A44" s="94"/>
       <c r="B44" s="47"/>
       <c r="C44" s="47"/>
       <c r="D44" s="95"/>
       <c r="E44" s="95"/>
       <c r="F44" s="96"/>
-      <c r="G44" s="143"/>
-      <c r="H44" s="143"/>
+      <c r="G44" s="173"/>
+      <c r="H44" s="173"/>
       <c r="I44" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16261,15 +16267,15 @@
       <c r="AE44" s="7"/>
       <c r="AF44" s="7"/>
     </row>
-    <row r="45" spans="1:32">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A45" s="94"/>
       <c r="B45" s="47"/>
       <c r="C45" s="47"/>
       <c r="D45" s="95"/>
       <c r="E45" s="95"/>
       <c r="F45" s="96"/>
-      <c r="G45" s="143"/>
-      <c r="H45" s="143"/>
+      <c r="G45" s="173"/>
+      <c r="H45" s="173"/>
       <c r="I45" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16322,15 +16328,15 @@
       <c r="AE45" s="7"/>
       <c r="AF45" s="7"/>
     </row>
-    <row r="46" spans="1:32">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A46" s="93"/>
       <c r="B46" s="47"/>
       <c r="C46" s="47"/>
       <c r="D46" s="97"/>
       <c r="E46" s="97"/>
       <c r="F46" s="96"/>
-      <c r="G46" s="143"/>
-      <c r="H46" s="143"/>
+      <c r="G46" s="173"/>
+      <c r="H46" s="173"/>
       <c r="I46" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16383,15 +16389,15 @@
       <c r="AE46" s="7"/>
       <c r="AF46" s="7"/>
     </row>
-    <row r="47" spans="1:32">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A47" s="93"/>
       <c r="B47" s="47"/>
       <c r="C47" s="47"/>
       <c r="D47" s="95"/>
       <c r="E47" s="95"/>
       <c r="F47" s="96"/>
-      <c r="G47" s="143"/>
-      <c r="H47" s="143"/>
+      <c r="G47" s="173"/>
+      <c r="H47" s="173"/>
       <c r="I47" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16444,15 +16450,15 @@
       <c r="AE47" s="7"/>
       <c r="AF47" s="7"/>
     </row>
-    <row r="48" spans="1:32">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A48" s="93"/>
       <c r="B48" s="47"/>
       <c r="C48" s="47"/>
       <c r="D48" s="95"/>
       <c r="E48" s="95"/>
       <c r="F48" s="96"/>
-      <c r="G48" s="143"/>
-      <c r="H48" s="143"/>
+      <c r="G48" s="173"/>
+      <c r="H48" s="173"/>
       <c r="I48" s="99" t="str">
         <f t="shared" ref="I48:I50" si="10">IF(D48=0,"",LOG($K$15*10^D48+$K$16*10^E48+$K$14))</f>
         <v/>
@@ -16505,15 +16511,15 @@
       <c r="AE48" s="7"/>
       <c r="AF48" s="7"/>
     </row>
-    <row r="49" spans="1:32">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A49" s="93"/>
       <c r="B49" s="47"/>
       <c r="C49" s="47"/>
       <c r="D49" s="95"/>
       <c r="E49" s="95"/>
       <c r="F49" s="96"/>
-      <c r="G49" s="143"/>
-      <c r="H49" s="143"/>
+      <c r="G49" s="173"/>
+      <c r="H49" s="173"/>
       <c r="I49" s="99" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -16566,15 +16572,15 @@
       <c r="AE49" s="7"/>
       <c r="AF49" s="7"/>
     </row>
-    <row r="50" spans="1:32">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A50" s="93"/>
       <c r="B50" s="47"/>
       <c r="C50" s="47"/>
       <c r="D50" s="95"/>
       <c r="E50" s="95"/>
       <c r="F50" s="96"/>
-      <c r="G50" s="143"/>
-      <c r="H50" s="143"/>
+      <c r="G50" s="173"/>
+      <c r="H50" s="173"/>
       <c r="I50" s="99" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -16627,15 +16633,15 @@
       <c r="AE50" s="7"/>
       <c r="AF50" s="7"/>
     </row>
-    <row r="51" spans="1:32">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A51" s="93"/>
       <c r="B51" s="47"/>
       <c r="C51" s="47"/>
       <c r="D51" s="95"/>
       <c r="E51" s="95"/>
       <c r="F51" s="96"/>
-      <c r="G51" s="143"/>
-      <c r="H51" s="143"/>
+      <c r="G51" s="173"/>
+      <c r="H51" s="173"/>
       <c r="I51" s="99" t="str">
         <f t="shared" ref="I51:I70" si="19">IF(D51=0,"",LOG($K$15*10^D51+$K$16*10^E51+$K$14))</f>
         <v/>
@@ -16688,15 +16694,15 @@
       <c r="AE51" s="7"/>
       <c r="AF51" s="7"/>
     </row>
-    <row r="52" spans="1:32">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A52" s="7"/>
       <c r="B52" s="47"/>
       <c r="C52" s="47"/>
       <c r="D52" s="48"/>
       <c r="E52" s="48"/>
       <c r="F52" s="96"/>
-      <c r="G52" s="143"/>
-      <c r="H52" s="143"/>
+      <c r="G52" s="173"/>
+      <c r="H52" s="173"/>
       <c r="I52" s="99" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -16749,15 +16755,15 @@
       <c r="AE52" s="7"/>
       <c r="AF52" s="7"/>
     </row>
-    <row r="53" spans="1:32">
+    <row r="53" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A53" s="7"/>
       <c r="B53" s="47"/>
       <c r="C53" s="47"/>
       <c r="D53" s="48"/>
       <c r="E53" s="48"/>
       <c r="F53" s="96"/>
-      <c r="G53" s="143"/>
-      <c r="H53" s="143"/>
+      <c r="G53" s="173"/>
+      <c r="H53" s="173"/>
       <c r="I53" s="99" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -16810,15 +16816,15 @@
       <c r="AE53" s="7"/>
       <c r="AF53" s="7"/>
     </row>
-    <row r="54" spans="1:32">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A54" s="7"/>
       <c r="B54" s="47"/>
       <c r="C54" s="47"/>
       <c r="D54" s="48"/>
       <c r="E54" s="48"/>
       <c r="F54" s="96"/>
-      <c r="G54" s="143"/>
-      <c r="H54" s="143"/>
+      <c r="G54" s="173"/>
+      <c r="H54" s="173"/>
       <c r="I54" s="99" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -16871,15 +16877,15 @@
       <c r="AE54" s="7"/>
       <c r="AF54" s="7"/>
     </row>
-    <row r="55" spans="1:32">
+    <row r="55" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A55" s="7"/>
       <c r="B55" s="47"/>
       <c r="C55" s="47"/>
       <c r="D55" s="48"/>
       <c r="E55" s="48"/>
       <c r="F55" s="58"/>
-      <c r="G55" s="143"/>
-      <c r="H55" s="143"/>
+      <c r="G55" s="173"/>
+      <c r="H55" s="173"/>
       <c r="I55" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -16932,15 +16938,15 @@
       <c r="AE55" s="7"/>
       <c r="AF55" s="7"/>
     </row>
-    <row r="56" spans="1:32">
+    <row r="56" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A56" s="7"/>
       <c r="B56" s="47"/>
       <c r="C56" s="47"/>
       <c r="D56" s="48"/>
       <c r="E56" s="48"/>
       <c r="F56" s="58"/>
-      <c r="G56" s="143"/>
-      <c r="H56" s="143"/>
+      <c r="G56" s="173"/>
+      <c r="H56" s="173"/>
       <c r="I56" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -16993,15 +16999,15 @@
       <c r="AE56" s="7"/>
       <c r="AF56" s="7"/>
     </row>
-    <row r="57" spans="1:32">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A57" s="7"/>
       <c r="B57" s="92"/>
       <c r="C57" s="92"/>
       <c r="D57" s="95"/>
       <c r="E57" s="95"/>
       <c r="F57" s="96"/>
-      <c r="G57" s="143"/>
-      <c r="H57" s="143"/>
+      <c r="G57" s="173"/>
+      <c r="H57" s="173"/>
       <c r="I57" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17054,15 +17060,15 @@
       <c r="AE57" s="7"/>
       <c r="AF57" s="7"/>
     </row>
-    <row r="58" spans="1:32">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A58" s="7"/>
       <c r="B58" s="47"/>
       <c r="C58" s="47"/>
       <c r="D58" s="48"/>
       <c r="E58" s="48"/>
       <c r="F58" s="58"/>
-      <c r="G58" s="143"/>
-      <c r="H58" s="143"/>
+      <c r="G58" s="173"/>
+      <c r="H58" s="173"/>
       <c r="I58" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17115,15 +17121,15 @@
       <c r="AE58" s="7"/>
       <c r="AF58" s="7"/>
     </row>
-    <row r="59" spans="1:32">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A59" s="7"/>
       <c r="B59" s="47"/>
       <c r="C59" s="47"/>
       <c r="D59" s="48"/>
       <c r="E59" s="48"/>
       <c r="F59" s="58"/>
-      <c r="G59" s="143"/>
-      <c r="H59" s="143"/>
+      <c r="G59" s="173"/>
+      <c r="H59" s="173"/>
       <c r="I59" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17176,15 +17182,15 @@
       <c r="AE59" s="7"/>
       <c r="AF59" s="7"/>
     </row>
-    <row r="60" spans="1:32">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A60" s="7"/>
       <c r="B60" s="47"/>
       <c r="C60" s="47"/>
       <c r="D60" s="48"/>
       <c r="E60" s="48"/>
       <c r="F60" s="58"/>
-      <c r="G60" s="143"/>
-      <c r="H60" s="143"/>
+      <c r="G60" s="173"/>
+      <c r="H60" s="173"/>
       <c r="I60" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17237,15 +17243,15 @@
       <c r="AE60" s="7"/>
       <c r="AF60" s="7"/>
     </row>
-    <row r="61" spans="1:32">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A61" s="7"/>
       <c r="B61" s="47"/>
       <c r="C61" s="47"/>
       <c r="D61" s="48"/>
       <c r="E61" s="48"/>
       <c r="F61" s="58"/>
-      <c r="G61" s="143"/>
-      <c r="H61" s="143"/>
+      <c r="G61" s="173"/>
+      <c r="H61" s="173"/>
       <c r="I61" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17298,15 +17304,15 @@
       <c r="AE61" s="7"/>
       <c r="AF61" s="7"/>
     </row>
-    <row r="62" spans="1:32">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A62" s="7"/>
       <c r="B62" s="47"/>
       <c r="C62" s="47"/>
       <c r="D62" s="48"/>
       <c r="E62" s="48"/>
       <c r="F62" s="58"/>
-      <c r="G62" s="143"/>
-      <c r="H62" s="143"/>
+      <c r="G62" s="173"/>
+      <c r="H62" s="173"/>
       <c r="I62" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17359,15 +17365,15 @@
       <c r="AE62" s="7"/>
       <c r="AF62" s="7"/>
     </row>
-    <row r="63" spans="1:32">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A63" s="7"/>
       <c r="B63" s="47"/>
       <c r="C63" s="47"/>
       <c r="D63" s="48"/>
       <c r="E63" s="48"/>
       <c r="F63" s="58"/>
-      <c r="G63" s="143"/>
-      <c r="H63" s="143"/>
+      <c r="G63" s="173"/>
+      <c r="H63" s="173"/>
       <c r="I63" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17420,15 +17426,15 @@
       <c r="AE63" s="7"/>
       <c r="AF63" s="7"/>
     </row>
-    <row r="64" spans="1:32">
+    <row r="64" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A64" s="7"/>
       <c r="B64" s="47"/>
       <c r="C64" s="47"/>
       <c r="D64" s="48"/>
       <c r="E64" s="48"/>
       <c r="F64" s="58"/>
-      <c r="G64" s="143"/>
-      <c r="H64" s="143"/>
+      <c r="G64" s="173"/>
+      <c r="H64" s="173"/>
       <c r="I64" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17481,15 +17487,15 @@
       <c r="AE64" s="7"/>
       <c r="AF64" s="7"/>
     </row>
-    <row r="65" spans="1:32">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A65" s="7"/>
       <c r="B65" s="47"/>
       <c r="C65" s="47"/>
       <c r="D65" s="48"/>
       <c r="E65" s="48"/>
       <c r="F65" s="58"/>
-      <c r="G65" s="143"/>
-      <c r="H65" s="143"/>
+      <c r="G65" s="173"/>
+      <c r="H65" s="173"/>
       <c r="I65" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17542,15 +17548,15 @@
       <c r="AE65" s="7"/>
       <c r="AF65" s="7"/>
     </row>
-    <row r="66" spans="1:32">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A66" s="7"/>
       <c r="B66" s="47"/>
       <c r="C66" s="47"/>
       <c r="D66" s="48"/>
       <c r="E66" s="48"/>
       <c r="F66" s="58"/>
-      <c r="G66" s="143"/>
-      <c r="H66" s="143"/>
+      <c r="G66" s="173"/>
+      <c r="H66" s="173"/>
       <c r="I66" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17603,15 +17609,15 @@
       <c r="AE66" s="7"/>
       <c r="AF66" s="7"/>
     </row>
-    <row r="67" spans="1:32">
+    <row r="67" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A67" s="7"/>
       <c r="B67" s="47"/>
       <c r="C67" s="47"/>
       <c r="D67" s="48"/>
       <c r="E67" s="48"/>
       <c r="F67" s="58"/>
-      <c r="G67" s="143"/>
-      <c r="H67" s="143"/>
+      <c r="G67" s="173"/>
+      <c r="H67" s="173"/>
       <c r="I67" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17664,15 +17670,15 @@
       <c r="AE67" s="7"/>
       <c r="AF67" s="7"/>
     </row>
-    <row r="68" spans="1:32">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A68" s="7"/>
       <c r="B68" s="47"/>
       <c r="C68" s="47"/>
       <c r="D68" s="48"/>
       <c r="E68" s="48"/>
       <c r="F68" s="58"/>
-      <c r="G68" s="143"/>
-      <c r="H68" s="143"/>
+      <c r="G68" s="173"/>
+      <c r="H68" s="173"/>
       <c r="I68" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17725,15 +17731,15 @@
       <c r="AE68" s="7"/>
       <c r="AF68" s="7"/>
     </row>
-    <row r="69" spans="1:32">
+    <row r="69" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A69" s="7"/>
       <c r="B69" s="47"/>
       <c r="C69" s="47"/>
       <c r="D69" s="48"/>
       <c r="E69" s="48"/>
       <c r="F69" s="58"/>
-      <c r="G69" s="143"/>
-      <c r="H69" s="143"/>
+      <c r="G69" s="173"/>
+      <c r="H69" s="173"/>
       <c r="I69" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17786,15 +17792,15 @@
       <c r="AE69" s="7"/>
       <c r="AF69" s="7"/>
     </row>
-    <row r="70" spans="1:32">
+    <row r="70" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A70" s="7"/>
       <c r="B70" s="47"/>
       <c r="C70" s="47"/>
       <c r="D70" s="48"/>
       <c r="E70" s="48"/>
       <c r="F70" s="58"/>
-      <c r="G70" s="143"/>
-      <c r="H70" s="143"/>
+      <c r="G70" s="173"/>
+      <c r="H70" s="173"/>
       <c r="I70" s="55" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17847,15 +17853,15 @@
       <c r="AE70" s="7"/>
       <c r="AF70" s="7"/>
     </row>
-    <row r="71" spans="1:32">
+    <row r="71" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A71" s="7"/>
       <c r="B71" s="47"/>
       <c r="C71" s="47"/>
       <c r="D71" s="48"/>
       <c r="E71" s="48"/>
       <c r="F71" s="58"/>
-      <c r="G71" s="143"/>
-      <c r="H71" s="143"/>
+      <c r="G71" s="173"/>
+      <c r="H71" s="173"/>
       <c r="I71" s="55" t="str">
         <f t="shared" ref="I71:I122" si="28">IF(D71=0,"",LOG($K$15*10^D71+$K$16*10^E71+$K$14))</f>
         <v/>
@@ -17908,15 +17914,15 @@
       <c r="AE71" s="7"/>
       <c r="AF71" s="7"/>
     </row>
-    <row r="72" spans="1:32">
+    <row r="72" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A72" s="7"/>
       <c r="B72" s="47"/>
       <c r="C72" s="47"/>
       <c r="D72" s="48"/>
       <c r="E72" s="48"/>
       <c r="F72" s="58"/>
-      <c r="G72" s="143"/>
-      <c r="H72" s="143"/>
+      <c r="G72" s="173"/>
+      <c r="H72" s="173"/>
       <c r="I72" s="55" t="str">
         <f t="shared" si="28"/>
         <v/>
@@ -17969,15 +17975,15 @@
       <c r="AE72" s="7"/>
       <c r="AF72" s="7"/>
     </row>
-    <row r="73" spans="1:32">
+    <row r="73" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A73" s="7"/>
       <c r="B73" s="47"/>
       <c r="C73" s="47"/>
       <c r="D73" s="48"/>
       <c r="E73" s="48"/>
       <c r="F73" s="58"/>
-      <c r="G73" s="143"/>
-      <c r="H73" s="143"/>
+      <c r="G73" s="173"/>
+      <c r="H73" s="173"/>
       <c r="I73" s="55" t="str">
         <f t="shared" si="28"/>
         <v/>
@@ -18030,15 +18036,15 @@
       <c r="AE73" s="7"/>
       <c r="AF73" s="7"/>
     </row>
-    <row r="74" spans="1:32">
+    <row r="74" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A74" s="7"/>
       <c r="B74" s="47"/>
       <c r="C74" s="47"/>
       <c r="D74" s="48"/>
       <c r="E74" s="48"/>
       <c r="F74" s="58"/>
-      <c r="G74" s="143"/>
-      <c r="H74" s="143"/>
+      <c r="G74" s="173"/>
+      <c r="H74" s="173"/>
       <c r="I74" s="55" t="str">
         <f t="shared" si="28"/>
         <v/>
@@ -18091,15 +18097,15 @@
       <c r="AE74" s="7"/>
       <c r="AF74" s="7"/>
     </row>
-    <row r="75" spans="1:32">
+    <row r="75" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A75" s="7"/>
       <c r="B75" s="47"/>
       <c r="C75" s="47"/>
       <c r="D75" s="48"/>
       <c r="E75" s="48"/>
       <c r="F75" s="58"/>
-      <c r="G75" s="143"/>
-      <c r="H75" s="143"/>
+      <c r="G75" s="173"/>
+      <c r="H75" s="173"/>
       <c r="I75" s="55" t="str">
         <f t="shared" si="28"/>
         <v/>
@@ -18152,15 +18158,15 @@
       <c r="AE75" s="7"/>
       <c r="AF75" s="7"/>
     </row>
-    <row r="76" spans="1:32">
+    <row r="76" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A76" s="7"/>
       <c r="B76" s="47"/>
       <c r="C76" s="47"/>
       <c r="D76" s="48"/>
       <c r="E76" s="48"/>
       <c r="F76" s="58"/>
-      <c r="G76" s="143"/>
-      <c r="H76" s="143"/>
+      <c r="G76" s="173"/>
+      <c r="H76" s="173"/>
       <c r="I76" s="55" t="str">
         <f t="shared" si="28"/>
         <v/>
@@ -18213,15 +18219,15 @@
       <c r="AE76" s="7"/>
       <c r="AF76" s="7"/>
     </row>
-    <row r="77" spans="1:32">
+    <row r="77" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A77" s="7"/>
       <c r="B77" s="47"/>
       <c r="C77" s="47"/>
       <c r="D77" s="48"/>
       <c r="E77" s="48"/>
       <c r="F77" s="58"/>
-      <c r="G77" s="143"/>
-      <c r="H77" s="143"/>
+      <c r="G77" s="173"/>
+      <c r="H77" s="173"/>
       <c r="I77" s="55" t="str">
         <f t="shared" si="28"/>
         <v/>
@@ -18274,7 +18280,7 @@
       <c r="AE77" s="7"/>
       <c r="AF77" s="7"/>
     </row>
-    <row r="78" spans="1:32">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A78" s="7"/>
       <c r="B78" s="47"/>
       <c r="C78" s="47"/>
@@ -18335,7 +18341,7 @@
       <c r="AE78" s="7"/>
       <c r="AF78" s="7"/>
     </row>
-    <row r="79" spans="1:32">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A79" s="7"/>
       <c r="B79" s="47"/>
       <c r="C79" s="47"/>
@@ -18396,7 +18402,7 @@
       <c r="AE79" s="7"/>
       <c r="AF79" s="7"/>
     </row>
-    <row r="80" spans="1:32">
+    <row r="80" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A80" s="7"/>
       <c r="B80" s="47"/>
       <c r="C80" s="47"/>
@@ -18457,7 +18463,7 @@
       <c r="AE80" s="7"/>
       <c r="AF80" s="7"/>
     </row>
-    <row r="81" spans="1:32">
+    <row r="81" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A81" s="7"/>
       <c r="B81" s="47"/>
       <c r="C81" s="47"/>
@@ -18518,7 +18524,7 @@
       <c r="AE81" s="7"/>
       <c r="AF81" s="7"/>
     </row>
-    <row r="82" spans="1:32">
+    <row r="82" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A82" s="7"/>
       <c r="B82" s="47"/>
       <c r="C82" s="47"/>
@@ -18579,7 +18585,7 @@
       <c r="AE82" s="7"/>
       <c r="AF82" s="7"/>
     </row>
-    <row r="83" spans="1:32">
+    <row r="83" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A83" s="7"/>
       <c r="B83" s="47"/>
       <c r="C83" s="47"/>
@@ -18640,7 +18646,7 @@
       <c r="AE83" s="7"/>
       <c r="AF83" s="7"/>
     </row>
-    <row r="84" spans="1:32">
+    <row r="84" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A84" s="7"/>
       <c r="B84" s="47"/>
       <c r="C84" s="47"/>
@@ -18701,7 +18707,7 @@
       <c r="AE84" s="7"/>
       <c r="AF84" s="7"/>
     </row>
-    <row r="85" spans="1:32">
+    <row r="85" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A85" s="7"/>
       <c r="B85" s="47"/>
       <c r="C85" s="47"/>
@@ -18762,7 +18768,7 @@
       <c r="AE85" s="7"/>
       <c r="AF85" s="7"/>
     </row>
-    <row r="86" spans="1:32">
+    <row r="86" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A86" s="7"/>
       <c r="B86" s="47"/>
       <c r="C86" s="47"/>
@@ -18823,7 +18829,7 @@
       <c r="AE86" s="7"/>
       <c r="AF86" s="7"/>
     </row>
-    <row r="87" spans="1:32">
+    <row r="87" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A87" s="7"/>
       <c r="B87" s="47"/>
       <c r="C87" s="47"/>
@@ -18884,7 +18890,7 @@
       <c r="AE87" s="7"/>
       <c r="AF87" s="7"/>
     </row>
-    <row r="88" spans="1:32">
+    <row r="88" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A88" s="7"/>
       <c r="B88" s="47"/>
       <c r="C88" s="47"/>
@@ -18945,7 +18951,7 @@
       <c r="AE88" s="7"/>
       <c r="AF88" s="7"/>
     </row>
-    <row r="89" spans="1:32">
+    <row r="89" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A89" s="7"/>
       <c r="B89" s="47"/>
       <c r="C89" s="47"/>
@@ -19006,7 +19012,7 @@
       <c r="AE89" s="7"/>
       <c r="AF89" s="7"/>
     </row>
-    <row r="90" spans="1:32">
+    <row r="90" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A90" s="7"/>
       <c r="B90" s="47"/>
       <c r="C90" s="47"/>
@@ -19067,7 +19073,7 @@
       <c r="AE90" s="7"/>
       <c r="AF90" s="7"/>
     </row>
-    <row r="91" spans="1:32">
+    <row r="91" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A91" s="7"/>
       <c r="B91" s="47"/>
       <c r="C91" s="47"/>
@@ -19128,7 +19134,7 @@
       <c r="AE91" s="7"/>
       <c r="AF91" s="7"/>
     </row>
-    <row r="92" spans="1:32">
+    <row r="92" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A92" s="7"/>
       <c r="B92" s="47"/>
       <c r="C92" s="47"/>
@@ -19189,7 +19195,7 @@
       <c r="AE92" s="7"/>
       <c r="AF92" s="7"/>
     </row>
-    <row r="93" spans="1:32">
+    <row r="93" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A93" s="7"/>
       <c r="B93" s="47"/>
       <c r="C93" s="47"/>
@@ -19250,7 +19256,7 @@
       <c r="AE93" s="7"/>
       <c r="AF93" s="7"/>
     </row>
-    <row r="94" spans="1:32">
+    <row r="94" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A94" s="7"/>
       <c r="B94" s="47"/>
       <c r="C94" s="47"/>
@@ -19311,7 +19317,7 @@
       <c r="AE94" s="7"/>
       <c r="AF94" s="7"/>
     </row>
-    <row r="95" spans="1:32">
+    <row r="95" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A95" s="7"/>
       <c r="B95" s="47"/>
       <c r="C95" s="47"/>
@@ -19372,7 +19378,7 @@
       <c r="AE95" s="7"/>
       <c r="AF95" s="7"/>
     </row>
-    <row r="96" spans="1:32">
+    <row r="96" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A96" s="7"/>
       <c r="B96" s="47"/>
       <c r="C96" s="47"/>
@@ -19433,7 +19439,7 @@
       <c r="AE96" s="7"/>
       <c r="AF96" s="7"/>
     </row>
-    <row r="97" spans="1:32">
+    <row r="97" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A97" s="7"/>
       <c r="B97" s="47"/>
       <c r="C97" s="47"/>
@@ -19494,7 +19500,7 @@
       <c r="AE97" s="7"/>
       <c r="AF97" s="7"/>
     </row>
-    <row r="98" spans="1:32">
+    <row r="98" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A98" s="7"/>
       <c r="B98" s="47"/>
       <c r="C98" s="47"/>
@@ -19555,7 +19561,7 @@
       <c r="AE98" s="7"/>
       <c r="AF98" s="7"/>
     </row>
-    <row r="99" spans="1:32">
+    <row r="99" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A99" s="7"/>
       <c r="B99" s="47"/>
       <c r="C99" s="47"/>
@@ -19616,7 +19622,7 @@
       <c r="AE99" s="7"/>
       <c r="AF99" s="7"/>
     </row>
-    <row r="100" spans="1:32">
+    <row r="100" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A100" s="7"/>
       <c r="B100" s="47"/>
       <c r="C100" s="47"/>
@@ -19677,7 +19683,7 @@
       <c r="AE100" s="7"/>
       <c r="AF100" s="7"/>
     </row>
-    <row r="101" spans="1:32">
+    <row r="101" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A101" s="7"/>
       <c r="B101" s="47"/>
       <c r="C101" s="47"/>
@@ -19738,7 +19744,7 @@
       <c r="AE101" s="7"/>
       <c r="AF101" s="7"/>
     </row>
-    <row r="102" spans="1:32">
+    <row r="102" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A102" s="7"/>
       <c r="B102" s="47"/>
       <c r="C102" s="47"/>
@@ -19799,7 +19805,7 @@
       <c r="AE102" s="7"/>
       <c r="AF102" s="7"/>
     </row>
-    <row r="103" spans="1:32">
+    <row r="103" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A103" s="7"/>
       <c r="B103" s="47"/>
       <c r="C103" s="47"/>
@@ -19860,7 +19866,7 @@
       <c r="AE103" s="7"/>
       <c r="AF103" s="7"/>
     </row>
-    <row r="104" spans="1:32">
+    <row r="104" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A104" s="7"/>
       <c r="B104" s="47"/>
       <c r="C104" s="47"/>
@@ -19921,7 +19927,7 @@
       <c r="AE104" s="7"/>
       <c r="AF104" s="7"/>
     </row>
-    <row r="105" spans="1:32">
+    <row r="105" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A105" s="7"/>
       <c r="B105" s="47"/>
       <c r="C105" s="47"/>
@@ -19982,7 +19988,7 @@
       <c r="AE105" s="7"/>
       <c r="AF105" s="7"/>
     </row>
-    <row r="106" spans="1:32">
+    <row r="106" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A106" s="7"/>
       <c r="B106" s="47"/>
       <c r="C106" s="47"/>
@@ -20043,7 +20049,7 @@
       <c r="AE106" s="7"/>
       <c r="AF106" s="7"/>
     </row>
-    <row r="107" spans="1:32">
+    <row r="107" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A107" s="7"/>
       <c r="B107" s="47"/>
       <c r="C107" s="47"/>
@@ -20104,7 +20110,7 @@
       <c r="AE107" s="7"/>
       <c r="AF107" s="7"/>
     </row>
-    <row r="108" spans="1:32">
+    <row r="108" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A108" s="7"/>
       <c r="B108" s="47"/>
       <c r="C108" s="47"/>
@@ -20165,7 +20171,7 @@
       <c r="AE108" s="7"/>
       <c r="AF108" s="7"/>
     </row>
-    <row r="109" spans="1:32">
+    <row r="109" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A109" s="7"/>
       <c r="B109" s="47"/>
       <c r="C109" s="47"/>
@@ -20226,7 +20232,7 @@
       <c r="AE109" s="7"/>
       <c r="AF109" s="7"/>
     </row>
-    <row r="110" spans="1:32">
+    <row r="110" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A110" s="7"/>
       <c r="B110" s="47"/>
       <c r="C110" s="47"/>
@@ -20287,7 +20293,7 @@
       <c r="AE110" s="7"/>
       <c r="AF110" s="7"/>
     </row>
-    <row r="111" spans="1:32">
+    <row r="111" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A111" s="7"/>
       <c r="B111" s="47"/>
       <c r="C111" s="47"/>
@@ -20348,7 +20354,7 @@
       <c r="AE111" s="7"/>
       <c r="AF111" s="7"/>
     </row>
-    <row r="112" spans="1:32">
+    <row r="112" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A112" s="7"/>
       <c r="B112" s="47"/>
       <c r="C112" s="47"/>
@@ -20409,7 +20415,7 @@
       <c r="AE112" s="7"/>
       <c r="AF112" s="7"/>
     </row>
-    <row r="113" spans="1:32">
+    <row r="113" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A113" s="7"/>
       <c r="B113" s="47"/>
       <c r="C113" s="47"/>
@@ -20470,7 +20476,7 @@
       <c r="AE113" s="7"/>
       <c r="AF113" s="7"/>
     </row>
-    <row r="114" spans="1:32">
+    <row r="114" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A114" s="7"/>
       <c r="B114" s="47"/>
       <c r="C114" s="47"/>
@@ -20531,7 +20537,7 @@
       <c r="AE114" s="7"/>
       <c r="AF114" s="7"/>
     </row>
-    <row r="115" spans="1:32">
+    <row r="115" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A115" s="7"/>
       <c r="B115" s="47"/>
       <c r="C115" s="47"/>
@@ -20592,7 +20598,7 @@
       <c r="AE115" s="7"/>
       <c r="AF115" s="7"/>
     </row>
-    <row r="116" spans="1:32">
+    <row r="116" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A116" s="7"/>
       <c r="B116" s="47"/>
       <c r="C116" s="47"/>
@@ -20653,7 +20659,7 @@
       <c r="AE116" s="7"/>
       <c r="AF116" s="7"/>
     </row>
-    <row r="117" spans="1:32">
+    <row r="117" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A117" s="7"/>
       <c r="B117" s="47"/>
       <c r="C117" s="47"/>
@@ -20714,7 +20720,7 @@
       <c r="AE117" s="7"/>
       <c r="AF117" s="7"/>
     </row>
-    <row r="118" spans="1:32">
+    <row r="118" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A118" s="7"/>
       <c r="B118" s="47"/>
       <c r="C118" s="47"/>
@@ -20775,7 +20781,7 @@
       <c r="AE118" s="7"/>
       <c r="AF118" s="7"/>
     </row>
-    <row r="119" spans="1:32">
+    <row r="119" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A119" s="7"/>
       <c r="B119" s="47"/>
       <c r="C119" s="47"/>
@@ -20836,7 +20842,7 @@
       <c r="AE119" s="7"/>
       <c r="AF119" s="7"/>
     </row>
-    <row r="120" spans="1:32">
+    <row r="120" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A120" s="7"/>
       <c r="B120" s="47"/>
       <c r="C120" s="47"/>
@@ -20897,7 +20903,7 @@
       <c r="AE120" s="7"/>
       <c r="AF120" s="7"/>
     </row>
-    <row r="121" spans="1:32">
+    <row r="121" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A121" s="7"/>
       <c r="B121" s="47"/>
       <c r="C121" s="47"/>
@@ -20958,7 +20964,7 @@
       <c r="AE121" s="7"/>
       <c r="AF121" s="7"/>
     </row>
-    <row r="122" spans="1:32">
+    <row r="122" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A122" s="7"/>
       <c r="B122" s="47"/>
       <c r="C122" s="47"/>
@@ -21019,7 +21025,7 @@
       <c r="AE122" s="7"/>
       <c r="AF122" s="7"/>
     </row>
-    <row r="123" spans="1:32">
+    <row r="123" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A123" s="7"/>
       <c r="B123" s="47"/>
       <c r="C123" s="47"/>
@@ -21080,7 +21086,7 @@
       <c r="AE123" s="7"/>
       <c r="AF123" s="7"/>
     </row>
-    <row r="124" spans="1:32">
+    <row r="124" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A124" s="7"/>
       <c r="B124" s="47"/>
       <c r="C124" s="47"/>
@@ -21141,7 +21147,7 @@
       <c r="AE124" s="7"/>
       <c r="AF124" s="7"/>
     </row>
-    <row r="125" spans="1:32">
+    <row r="125" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A125" s="7"/>
       <c r="B125" s="47"/>
       <c r="C125" s="47"/>
@@ -21202,7 +21208,7 @@
       <c r="AE125" s="7"/>
       <c r="AF125" s="7"/>
     </row>
-    <row r="126" spans="1:32">
+    <row r="126" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A126" s="7"/>
       <c r="B126" s="47"/>
       <c r="C126" s="47"/>
@@ -21263,7 +21269,7 @@
       <c r="AE126" s="7"/>
       <c r="AF126" s="7"/>
     </row>
-    <row r="127" spans="1:32">
+    <row r="127" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A127" s="7"/>
       <c r="B127" s="47"/>
       <c r="C127" s="47"/>
@@ -21324,7 +21330,7 @@
       <c r="AE127" s="7"/>
       <c r="AF127" s="7"/>
     </row>
-    <row r="128" spans="1:32">
+    <row r="128" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A128" s="7"/>
       <c r="B128" s="82" t="s">
         <v>72</v>
@@ -21362,7 +21368,7 @@
       <c r="AE128" s="7"/>
       <c r="AF128" s="7"/>
     </row>
-    <row r="129" spans="1:32">
+    <row r="129" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A129" s="7"/>
       <c r="B129" s="49"/>
       <c r="C129" s="49"/>
@@ -21396,7 +21402,7 @@
       <c r="AE129" s="7"/>
       <c r="AF129" s="7"/>
     </row>
-    <row r="130" spans="1:32">
+    <row r="130" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A130" s="7"/>
       <c r="B130" s="49"/>
       <c r="C130" s="49"/>
@@ -21430,7 +21436,7 @@
       <c r="AE130" s="7"/>
       <c r="AF130" s="7"/>
     </row>
-    <row r="131" spans="1:32">
+    <row r="131" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A131" s="7"/>
       <c r="B131" s="49"/>
       <c r="C131" s="49"/>
@@ -21464,7 +21470,7 @@
       <c r="AE131" s="7"/>
       <c r="AF131" s="7"/>
     </row>
-    <row r="132" spans="1:32">
+    <row r="132" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A132" s="7"/>
       <c r="B132" s="49"/>
       <c r="C132" s="49"/>
@@ -21498,7 +21504,7 @@
       <c r="AE132" s="7"/>
       <c r="AF132" s="7"/>
     </row>
-    <row r="133" spans="1:32">
+    <row r="133" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A133" s="7"/>
       <c r="B133" s="49"/>
       <c r="C133" s="49"/>
@@ -21532,7 +21538,7 @@
       <c r="AE133" s="7"/>
       <c r="AF133" s="7"/>
     </row>
-    <row r="134" spans="1:32">
+    <row r="134" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A134" s="7"/>
       <c r="B134" s="49"/>
       <c r="C134" s="49"/>
@@ -21566,7 +21572,7 @@
       <c r="AE134" s="7"/>
       <c r="AF134" s="7"/>
     </row>
-    <row r="135" spans="1:32">
+    <row r="135" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A135" s="7"/>
       <c r="B135" s="49"/>
       <c r="C135" s="49"/>
@@ -21600,7 +21606,7 @@
       <c r="AE135" s="7"/>
       <c r="AF135" s="7"/>
     </row>
-    <row r="136" spans="1:32">
+    <row r="136" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A136" s="7"/>
       <c r="B136" s="49"/>
       <c r="C136" s="49"/>
@@ -21634,7 +21640,7 @@
       <c r="AE136" s="7"/>
       <c r="AF136" s="7"/>
     </row>
-    <row r="137" spans="1:32">
+    <row r="137" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A137" s="7"/>
       <c r="B137" s="49"/>
       <c r="C137" s="49"/>
@@ -21668,7 +21674,7 @@
       <c r="AE137" s="7"/>
       <c r="AF137" s="7"/>
     </row>
-    <row r="138" spans="1:32">
+    <row r="138" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A138" s="7"/>
       <c r="B138" s="49"/>
       <c r="C138" s="49"/>
@@ -21702,7 +21708,7 @@
       <c r="AE138" s="7"/>
       <c r="AF138" s="7"/>
     </row>
-    <row r="139" spans="1:32">
+    <row r="139" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A139" s="7"/>
       <c r="B139" s="49"/>
       <c r="C139" s="49"/>
@@ -21736,7 +21742,7 @@
       <c r="AE139" s="7"/>
       <c r="AF139" s="7"/>
     </row>
-    <row r="140" spans="1:32">
+    <row r="140" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A140" s="7"/>
       <c r="B140" s="49"/>
       <c r="C140" s="49"/>
@@ -21770,7 +21776,7 @@
       <c r="AE140" s="7"/>
       <c r="AF140" s="7"/>
     </row>
-    <row r="141" spans="1:32">
+    <row r="141" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A141" s="7"/>
       <c r="B141" s="49"/>
       <c r="C141" s="49"/>
@@ -21804,7 +21810,7 @@
       <c r="AE141" s="7"/>
       <c r="AF141" s="7"/>
     </row>
-    <row r="142" spans="1:32">
+    <row r="142" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A142" s="7"/>
       <c r="B142" s="49"/>
       <c r="C142" s="49"/>
@@ -21838,7 +21844,7 @@
       <c r="AE142" s="7"/>
       <c r="AF142" s="7"/>
     </row>
-    <row r="143" spans="1:32">
+    <row r="143" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A143" s="7"/>
       <c r="B143" s="49"/>
       <c r="C143" s="49"/>
@@ -21872,7 +21878,7 @@
       <c r="AE143" s="7"/>
       <c r="AF143" s="7"/>
     </row>
-    <row r="144" spans="1:32">
+    <row r="144" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A144" s="7"/>
       <c r="B144" s="49"/>
       <c r="C144" s="49"/>
@@ -21906,7 +21912,7 @@
       <c r="AE144" s="7"/>
       <c r="AF144" s="7"/>
     </row>
-    <row r="145" spans="1:32">
+    <row r="145" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A145" s="7"/>
       <c r="B145" s="49"/>
       <c r="C145" s="49"/>
@@ -21940,7 +21946,7 @@
       <c r="AE145" s="7"/>
       <c r="AF145" s="7"/>
     </row>
-    <row r="146" spans="1:32">
+    <row r="146" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A146" s="7"/>
       <c r="B146" s="49"/>
       <c r="C146" s="49"/>
@@ -21974,7 +21980,7 @@
       <c r="AE146" s="7"/>
       <c r="AF146" s="7"/>
     </row>
-    <row r="147" spans="1:32">
+    <row r="147" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A147" s="7"/>
       <c r="B147" s="49"/>
       <c r="C147" s="49"/>
@@ -22008,7 +22014,7 @@
       <c r="AE147" s="7"/>
       <c r="AF147" s="7"/>
     </row>
-    <row r="148" spans="1:32">
+    <row r="148" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A148" s="7"/>
       <c r="B148" s="49"/>
       <c r="C148" s="49"/>
@@ -22042,7 +22048,7 @@
       <c r="AE148" s="7"/>
       <c r="AF148" s="7"/>
     </row>
-    <row r="149" spans="1:32">
+    <row r="149" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A149" s="7"/>
       <c r="B149" s="49"/>
       <c r="C149" s="49"/>
@@ -22076,7 +22082,7 @@
       <c r="AE149" s="7"/>
       <c r="AF149" s="7"/>
     </row>
-    <row r="150" spans="1:32">
+    <row r="150" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A150" s="7"/>
       <c r="B150" s="49"/>
       <c r="C150" s="49"/>
@@ -22110,7 +22116,7 @@
       <c r="AE150" s="7"/>
       <c r="AF150" s="7"/>
     </row>
-    <row r="151" spans="1:32">
+    <row r="151" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A151" s="7"/>
       <c r="B151" s="49"/>
       <c r="C151" s="49"/>
@@ -22144,7 +22150,7 @@
       <c r="AE151" s="7"/>
       <c r="AF151" s="7"/>
     </row>
-    <row r="152" spans="1:32">
+    <row r="152" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A152" s="7"/>
       <c r="B152" s="49"/>
       <c r="C152" s="49"/>
@@ -22178,7 +22184,7 @@
       <c r="AE152" s="7"/>
       <c r="AF152" s="7"/>
     </row>
-    <row r="153" spans="1:32">
+    <row r="153" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A153" s="7"/>
       <c r="B153" s="49"/>
       <c r="C153" s="49"/>
@@ -22212,7 +22218,7 @@
       <c r="AE153" s="7"/>
       <c r="AF153" s="7"/>
     </row>
-    <row r="154" spans="1:32">
+    <row r="154" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A154" s="7"/>
       <c r="B154" s="49"/>
       <c r="C154" s="49"/>
@@ -22246,7 +22252,7 @@
       <c r="AE154" s="7"/>
       <c r="AF154" s="7"/>
     </row>
-    <row r="155" spans="1:32">
+    <row r="155" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A155" s="7"/>
       <c r="B155" s="49"/>
       <c r="C155" s="49"/>
@@ -22280,7 +22286,7 @@
       <c r="AE155" s="7"/>
       <c r="AF155" s="7"/>
     </row>
-    <row r="156" spans="1:32">
+    <row r="156" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A156" s="7"/>
       <c r="B156" s="49"/>
       <c r="C156" s="49"/>
@@ -22314,7 +22320,7 @@
       <c r="AE156" s="7"/>
       <c r="AF156" s="7"/>
     </row>
-    <row r="157" spans="1:32">
+    <row r="157" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A157" s="7"/>
       <c r="B157" s="49"/>
       <c r="C157" s="49"/>
@@ -22348,7 +22354,7 @@
       <c r="AE157" s="7"/>
       <c r="AF157" s="7"/>
     </row>
-    <row r="158" spans="1:32">
+    <row r="158" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A158" s="7"/>
       <c r="B158" s="49"/>
       <c r="C158" s="49"/>
@@ -22382,7 +22388,7 @@
       <c r="AE158" s="7"/>
       <c r="AF158" s="7"/>
     </row>
-    <row r="159" spans="1:32">
+    <row r="159" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A159" s="7"/>
       <c r="B159" s="49"/>
       <c r="C159" s="49"/>
@@ -22416,7 +22422,7 @@
       <c r="AE159" s="7"/>
       <c r="AF159" s="7"/>
     </row>
-    <row r="160" spans="1:32">
+    <row r="160" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A160" s="7"/>
       <c r="B160" s="49"/>
       <c r="C160" s="49"/>
@@ -22450,7 +22456,7 @@
       <c r="AE160" s="7"/>
       <c r="AF160" s="7"/>
     </row>
-    <row r="161" spans="1:32">
+    <row r="161" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A161" s="7"/>
       <c r="B161" s="49"/>
       <c r="C161" s="49"/>
@@ -22484,7 +22490,7 @@
       <c r="AE161" s="7"/>
       <c r="AF161" s="7"/>
     </row>
-    <row r="162" spans="1:32">
+    <row r="162" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A162" s="7"/>
       <c r="B162" s="49"/>
       <c r="C162" s="49"/>
@@ -22518,7 +22524,7 @@
       <c r="AE162" s="7"/>
       <c r="AF162" s="7"/>
     </row>
-    <row r="163" spans="1:32">
+    <row r="163" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A163" s="7"/>
       <c r="B163" s="49"/>
       <c r="C163" s="49"/>
@@ -22552,7 +22558,7 @@
       <c r="AE163" s="7"/>
       <c r="AF163" s="7"/>
     </row>
-    <row r="164" spans="1:32">
+    <row r="164" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A164" s="7"/>
       <c r="B164" s="49"/>
       <c r="C164" s="49"/>
@@ -22586,7 +22592,7 @@
       <c r="AE164" s="7"/>
       <c r="AF164" s="7"/>
     </row>
-    <row r="165" spans="1:32">
+    <row r="165" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A165" s="7"/>
       <c r="B165" s="49"/>
       <c r="C165" s="49"/>
@@ -22620,7 +22626,7 @@
       <c r="AE165" s="7"/>
       <c r="AF165" s="7"/>
     </row>
-    <row r="166" spans="1:32">
+    <row r="166" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A166" s="7"/>
       <c r="B166" s="49"/>
       <c r="C166" s="49"/>
@@ -22654,7 +22660,7 @@
       <c r="AE166" s="7"/>
       <c r="AF166" s="7"/>
     </row>
-    <row r="167" spans="1:32">
+    <row r="167" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A167" s="7"/>
       <c r="B167" s="49"/>
       <c r="C167" s="49"/>
@@ -22688,7 +22694,7 @@
       <c r="AE167" s="7"/>
       <c r="AF167" s="7"/>
     </row>
-    <row r="168" spans="1:32">
+    <row r="168" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A168" s="7"/>
       <c r="B168" s="49"/>
       <c r="C168" s="49"/>
@@ -22722,7 +22728,7 @@
       <c r="AE168" s="7"/>
       <c r="AF168" s="7"/>
     </row>
-    <row r="169" spans="1:32">
+    <row r="169" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A169" s="7"/>
       <c r="B169" s="49"/>
       <c r="C169" s="49"/>
@@ -22756,7 +22762,7 @@
       <c r="AE169" s="7"/>
       <c r="AF169" s="7"/>
     </row>
-    <row r="170" spans="1:32">
+    <row r="170" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A170" s="7"/>
       <c r="B170" s="49"/>
       <c r="C170" s="49"/>
@@ -22790,7 +22796,7 @@
       <c r="AE170" s="7"/>
       <c r="AF170" s="7"/>
     </row>
-    <row r="171" spans="1:32">
+    <row r="171" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A171" s="7"/>
       <c r="B171" s="49"/>
       <c r="C171" s="49"/>
@@ -22824,7 +22830,7 @@
       <c r="AE171" s="7"/>
       <c r="AF171" s="7"/>
     </row>
-    <row r="172" spans="1:32">
+    <row r="172" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A172" s="7"/>
       <c r="B172" s="49"/>
       <c r="C172" s="49"/>
@@ -22858,7 +22864,7 @@
       <c r="AE172" s="7"/>
       <c r="AF172" s="7"/>
     </row>
-    <row r="173" spans="1:32">
+    <row r="173" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A173" s="7"/>
       <c r="B173" s="49"/>
       <c r="C173" s="49"/>
@@ -22892,7 +22898,7 @@
       <c r="AE173" s="7"/>
       <c r="AF173" s="7"/>
     </row>
-    <row r="174" spans="1:32">
+    <row r="174" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A174" s="7"/>
       <c r="B174" s="49"/>
       <c r="C174" s="49"/>
@@ -22926,7 +22932,7 @@
       <c r="AE174" s="7"/>
       <c r="AF174" s="7"/>
     </row>
-    <row r="175" spans="1:32">
+    <row r="175" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A175" s="7"/>
       <c r="B175" s="49"/>
       <c r="C175" s="49"/>
@@ -22960,7 +22966,7 @@
       <c r="AE175" s="7"/>
       <c r="AF175" s="7"/>
     </row>
-    <row r="176" spans="1:32">
+    <row r="176" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A176" s="7"/>
       <c r="B176" s="49"/>
       <c r="C176" s="49"/>
@@ -22994,7 +23000,7 @@
       <c r="AE176" s="7"/>
       <c r="AF176" s="7"/>
     </row>
-    <row r="177" spans="1:32">
+    <row r="177" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A177" s="7"/>
       <c r="B177" s="49"/>
       <c r="C177" s="49"/>
@@ -23028,7 +23034,7 @@
       <c r="AE177" s="7"/>
       <c r="AF177" s="7"/>
     </row>
-    <row r="178" spans="1:32">
+    <row r="178" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A178" s="7"/>
       <c r="B178" s="49"/>
       <c r="C178" s="49"/>
@@ -23062,7 +23068,7 @@
       <c r="AE178" s="7"/>
       <c r="AF178" s="7"/>
     </row>
-    <row r="179" spans="1:32">
+    <row r="179" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A179" s="7"/>
       <c r="B179" s="49"/>
       <c r="C179" s="49"/>
@@ -23096,7 +23102,7 @@
       <c r="AE179" s="7"/>
       <c r="AF179" s="7"/>
     </row>
-    <row r="180" spans="1:32">
+    <row r="180" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A180" s="7"/>
       <c r="B180" s="49"/>
       <c r="C180" s="49"/>
@@ -23130,7 +23136,7 @@
       <c r="AE180" s="7"/>
       <c r="AF180" s="7"/>
     </row>
-    <row r="181" spans="1:32">
+    <row r="181" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A181" s="7"/>
       <c r="B181" s="49"/>
       <c r="C181" s="49"/>
@@ -23164,7 +23170,7 @@
       <c r="AE181" s="7"/>
       <c r="AF181" s="7"/>
     </row>
-    <row r="182" spans="1:32">
+    <row r="182" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A182" s="7"/>
       <c r="B182" s="49"/>
       <c r="C182" s="49"/>
@@ -23198,7 +23204,7 @@
       <c r="AE182" s="7"/>
       <c r="AF182" s="7"/>
     </row>
-    <row r="183" spans="1:32">
+    <row r="183" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A183" s="7"/>
       <c r="B183" s="49"/>
       <c r="C183" s="49"/>
@@ -23232,7 +23238,7 @@
       <c r="AE183" s="7"/>
       <c r="AF183" s="7"/>
     </row>
-    <row r="184" spans="1:32">
+    <row r="184" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A184" s="7"/>
       <c r="B184" s="49"/>
       <c r="C184" s="49"/>
@@ -23266,7 +23272,7 @@
       <c r="AE184" s="7"/>
       <c r="AF184" s="7"/>
     </row>
-    <row r="185" spans="1:32">
+    <row r="185" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A185" s="7"/>
       <c r="B185" s="49"/>
       <c r="C185" s="49"/>
@@ -23300,7 +23306,7 @@
       <c r="AE185" s="7"/>
       <c r="AF185" s="7"/>
     </row>
-    <row r="186" spans="1:32">
+    <row r="186" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A186" s="7"/>
       <c r="B186" s="49"/>
       <c r="C186" s="49"/>
@@ -23334,7 +23340,7 @@
       <c r="AE186" s="7"/>
       <c r="AF186" s="7"/>
     </row>
-    <row r="187" spans="1:32">
+    <row r="187" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A187" s="7"/>
       <c r="B187" s="49"/>
       <c r="C187" s="49"/>
@@ -23368,7 +23374,7 @@
       <c r="AE187" s="7"/>
       <c r="AF187" s="7"/>
     </row>
-    <row r="188" spans="1:32">
+    <row r="188" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A188" s="7"/>
       <c r="B188" s="49"/>
       <c r="C188" s="49"/>
@@ -23402,7 +23408,7 @@
       <c r="AE188" s="7"/>
       <c r="AF188" s="7"/>
     </row>
-    <row r="189" spans="1:32">
+    <row r="189" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A189" s="7"/>
       <c r="B189" s="49"/>
       <c r="C189" s="49"/>
@@ -23436,7 +23442,7 @@
       <c r="AE189" s="7"/>
       <c r="AF189" s="7"/>
     </row>
-    <row r="190" spans="1:32">
+    <row r="190" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A190" s="7"/>
       <c r="B190" s="49"/>
       <c r="C190" s="49"/>
@@ -23470,7 +23476,7 @@
       <c r="AE190" s="7"/>
       <c r="AF190" s="7"/>
     </row>
-    <row r="191" spans="1:32">
+    <row r="191" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A191" s="7"/>
       <c r="B191" s="49"/>
       <c r="C191" s="49"/>
@@ -23504,7 +23510,7 @@
       <c r="AE191" s="7"/>
       <c r="AF191" s="7"/>
     </row>
-    <row r="192" spans="1:32">
+    <row r="192" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A192" s="7"/>
       <c r="B192" s="49"/>
       <c r="C192" s="49"/>
@@ -23538,7 +23544,7 @@
       <c r="AE192" s="7"/>
       <c r="AF192" s="7"/>
     </row>
-    <row r="193" spans="1:32">
+    <row r="193" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A193" s="7"/>
       <c r="B193" s="49"/>
       <c r="C193" s="49"/>
@@ -23572,7 +23578,7 @@
       <c r="AE193" s="7"/>
       <c r="AF193" s="7"/>
     </row>
-    <row r="194" spans="1:32">
+    <row r="194" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A194" s="7"/>
       <c r="B194" s="49"/>
       <c r="C194" s="49"/>
@@ -23606,7 +23612,7 @@
       <c r="AE194" s="7"/>
       <c r="AF194" s="7"/>
     </row>
-    <row r="195" spans="1:32">
+    <row r="195" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A195" s="7"/>
       <c r="B195" s="49"/>
       <c r="C195" s="49"/>
@@ -23640,7 +23646,7 @@
       <c r="AE195" s="7"/>
       <c r="AF195" s="7"/>
     </row>
-    <row r="196" spans="1:32">
+    <row r="196" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A196" s="7"/>
       <c r="B196" s="49"/>
       <c r="C196" s="49"/>
@@ -23674,7 +23680,7 @@
       <c r="AE196" s="7"/>
       <c r="AF196" s="7"/>
     </row>
-    <row r="197" spans="1:32">
+    <row r="197" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A197" s="7"/>
       <c r="B197" s="49"/>
       <c r="C197" s="49"/>
@@ -23708,7 +23714,7 @@
       <c r="AE197" s="7"/>
       <c r="AF197" s="7"/>
     </row>
-    <row r="198" spans="1:32">
+    <row r="198" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A198" s="7"/>
       <c r="B198" s="49"/>
       <c r="C198" s="49"/>
@@ -23742,7 +23748,7 @@
       <c r="AE198" s="7"/>
       <c r="AF198" s="7"/>
     </row>
-    <row r="199" spans="1:32">
+    <row r="199" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A199" s="7"/>
       <c r="B199" s="49"/>
       <c r="C199" s="49"/>
@@ -23776,7 +23782,7 @@
       <c r="AE199" s="7"/>
       <c r="AF199" s="7"/>
     </row>
-    <row r="200" spans="1:32">
+    <row r="200" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A200" s="7"/>
       <c r="B200" s="49"/>
       <c r="C200" s="49"/>
@@ -23810,7 +23816,7 @@
       <c r="AE200" s="7"/>
       <c r="AF200" s="7"/>
     </row>
-    <row r="201" spans="1:32">
+    <row r="201" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A201" s="7"/>
       <c r="B201" s="49"/>
       <c r="C201" s="49"/>
@@ -23844,7 +23850,7 @@
       <c r="AE201" s="7"/>
       <c r="AF201" s="7"/>
     </row>
-    <row r="202" spans="1:32">
+    <row r="202" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A202" s="7"/>
       <c r="B202" s="49"/>
       <c r="C202" s="49"/>
@@ -23878,7 +23884,7 @@
       <c r="AE202" s="7"/>
       <c r="AF202" s="7"/>
     </row>
-    <row r="203" spans="1:32">
+    <row r="203" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A203" s="7"/>
       <c r="B203" s="49"/>
       <c r="C203" s="49"/>
@@ -23912,7 +23918,7 @@
       <c r="AE203" s="7"/>
       <c r="AF203" s="7"/>
     </row>
-    <row r="204" spans="1:32">
+    <row r="204" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A204" s="7"/>
       <c r="B204" s="49"/>
       <c r="C204" s="49"/>
@@ -23946,7 +23952,7 @@
       <c r="AE204" s="7"/>
       <c r="AF204" s="7"/>
     </row>
-    <row r="205" spans="1:32">
+    <row r="205" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A205" s="7"/>
       <c r="B205" s="49"/>
       <c r="C205" s="49"/>
@@ -23980,7 +23986,7 @@
       <c r="AE205" s="7"/>
       <c r="AF205" s="7"/>
     </row>
-    <row r="206" spans="1:32">
+    <row r="206" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A206" s="7"/>
       <c r="B206" s="49"/>
       <c r="C206" s="49"/>
@@ -24014,7 +24020,7 @@
       <c r="AE206" s="7"/>
       <c r="AF206" s="7"/>
     </row>
-    <row r="207" spans="1:32">
+    <row r="207" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A207" s="7"/>
       <c r="B207" s="49"/>
       <c r="C207" s="49"/>
@@ -24048,7 +24054,7 @@
       <c r="AE207" s="7"/>
       <c r="AF207" s="7"/>
     </row>
-    <row r="208" spans="1:32">
+    <row r="208" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A208" s="7"/>
       <c r="B208" s="49"/>
       <c r="C208" s="49"/>
@@ -24082,7 +24088,7 @@
       <c r="AE208" s="7"/>
       <c r="AF208" s="7"/>
     </row>
-    <row r="209" spans="1:32">
+    <row r="209" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A209" s="7"/>
       <c r="B209" s="49"/>
       <c r="C209" s="49"/>
@@ -24116,7 +24122,7 @@
       <c r="AE209" s="7"/>
       <c r="AF209" s="7"/>
     </row>
-    <row r="210" spans="1:32">
+    <row r="210" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A210" s="7"/>
       <c r="B210" s="49"/>
       <c r="C210" s="49"/>
@@ -24150,7 +24156,7 @@
       <c r="AE210" s="7"/>
       <c r="AF210" s="7"/>
     </row>
-    <row r="211" spans="1:32">
+    <row r="211" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A211" s="7"/>
       <c r="B211" s="49"/>
       <c r="C211" s="49"/>
@@ -24184,7 +24190,7 @@
       <c r="AE211" s="7"/>
       <c r="AF211" s="7"/>
     </row>
-    <row r="212" spans="1:32">
+    <row r="212" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A212" s="7"/>
       <c r="B212" s="49"/>
       <c r="C212" s="49"/>
@@ -24218,7 +24224,7 @@
       <c r="AE212" s="7"/>
       <c r="AF212" s="7"/>
     </row>
-    <row r="213" spans="1:32">
+    <row r="213" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A213" s="7"/>
       <c r="B213" s="49"/>
       <c r="C213" s="49"/>
@@ -24252,7 +24258,7 @@
       <c r="AE213" s="7"/>
       <c r="AF213" s="7"/>
     </row>
-    <row r="214" spans="1:32">
+    <row r="214" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A214" s="7"/>
       <c r="B214" s="49"/>
       <c r="C214" s="49"/>
@@ -24286,7 +24292,7 @@
       <c r="AE214" s="7"/>
       <c r="AF214" s="7"/>
     </row>
-    <row r="215" spans="1:32">
+    <row r="215" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A215" s="7"/>
       <c r="B215" s="49"/>
       <c r="C215" s="49"/>
@@ -24320,7 +24326,7 @@
       <c r="AE215" s="7"/>
       <c r="AF215" s="7"/>
     </row>
-    <row r="216" spans="1:32">
+    <row r="216" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A216" s="7"/>
       <c r="B216" s="49"/>
       <c r="C216" s="49"/>
@@ -24354,7 +24360,7 @@
       <c r="AE216" s="7"/>
       <c r="AF216" s="7"/>
     </row>
-    <row r="217" spans="1:32">
+    <row r="217" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A217" s="7"/>
       <c r="B217" s="49"/>
       <c r="C217" s="49"/>
@@ -24388,7 +24394,7 @@
       <c r="AE217" s="7"/>
       <c r="AF217" s="7"/>
     </row>
-    <row r="218" spans="1:32">
+    <row r="218" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A218" s="7"/>
       <c r="B218" s="49"/>
       <c r="C218" s="49"/>
@@ -24422,7 +24428,7 @@
       <c r="AE218" s="7"/>
       <c r="AF218" s="7"/>
     </row>
-    <row r="219" spans="1:32">
+    <row r="219" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A219" s="7"/>
       <c r="B219" s="49"/>
       <c r="C219" s="49"/>
@@ -24456,7 +24462,7 @@
       <c r="AE219" s="7"/>
       <c r="AF219" s="7"/>
     </row>
-    <row r="220" spans="1:32">
+    <row r="220" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A220" s="7"/>
       <c r="B220" s="49"/>
       <c r="C220" s="49"/>
@@ -24490,7 +24496,7 @@
       <c r="AE220" s="7"/>
       <c r="AF220" s="7"/>
     </row>
-    <row r="221" spans="1:32">
+    <row r="221" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A221" s="7"/>
       <c r="B221" s="49"/>
       <c r="C221" s="49"/>
@@ -24524,7 +24530,7 @@
       <c r="AE221" s="7"/>
       <c r="AF221" s="7"/>
     </row>
-    <row r="222" spans="1:32">
+    <row r="222" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A222" s="7"/>
       <c r="B222" s="49"/>
       <c r="C222" s="49"/>
@@ -24558,7 +24564,7 @@
       <c r="AE222" s="7"/>
       <c r="AF222" s="7"/>
     </row>
-    <row r="223" spans="1:32">
+    <row r="223" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A223" s="7"/>
       <c r="B223" s="49"/>
       <c r="C223" s="49"/>
@@ -24592,7 +24598,7 @@
       <c r="AE223" s="7"/>
       <c r="AF223" s="7"/>
     </row>
-    <row r="224" spans="1:32">
+    <row r="224" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A224" s="7"/>
       <c r="B224" s="49"/>
       <c r="C224" s="49"/>
@@ -24626,7 +24632,7 @@
       <c r="AE224" s="7"/>
       <c r="AF224" s="7"/>
     </row>
-    <row r="225" spans="1:32">
+    <row r="225" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A225" s="7"/>
       <c r="B225" s="49"/>
       <c r="C225" s="49"/>
@@ -24660,7 +24666,7 @@
       <c r="AE225" s="7"/>
       <c r="AF225" s="7"/>
     </row>
-    <row r="226" spans="1:32">
+    <row r="226" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A226" s="7"/>
       <c r="B226" s="49"/>
       <c r="C226" s="49"/>
@@ -24694,7 +24700,7 @@
       <c r="AE226" s="7"/>
       <c r="AF226" s="7"/>
     </row>
-    <row r="227" spans="1:32">
+    <row r="227" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A227" s="7"/>
       <c r="B227" s="49"/>
       <c r="C227" s="49"/>
@@ -24728,7 +24734,7 @@
       <c r="AE227" s="7"/>
       <c r="AF227" s="7"/>
     </row>
-    <row r="228" spans="1:32">
+    <row r="228" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A228" s="7"/>
       <c r="B228" s="49"/>
       <c r="C228" s="49"/>
@@ -24762,7 +24768,7 @@
       <c r="AE228" s="7"/>
       <c r="AF228" s="7"/>
     </row>
-    <row r="229" spans="1:32">
+    <row r="229" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A229" s="7"/>
       <c r="B229" s="49"/>
       <c r="C229" s="49"/>
@@ -24796,7 +24802,7 @@
       <c r="AE229" s="7"/>
       <c r="AF229" s="7"/>
     </row>
-    <row r="230" spans="1:32">
+    <row r="230" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A230" s="7"/>
       <c r="B230" s="7"/>
       <c r="C230" s="7"/>
@@ -24830,7 +24836,7 @@
       <c r="AE230" s="7"/>
       <c r="AF230" s="7"/>
     </row>
-    <row r="231" spans="1:32">
+    <row r="231" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A231" s="7"/>
       <c r="B231" s="7"/>
       <c r="C231" s="7"/>
@@ -24864,7 +24870,7 @@
       <c r="AE231" s="7"/>
       <c r="AF231" s="7"/>
     </row>
-    <row r="232" spans="1:32">
+    <row r="232" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A232" s="7"/>
       <c r="B232" s="7"/>
       <c r="C232" s="7"/>
@@ -24898,7 +24904,7 @@
       <c r="AE232" s="7"/>
       <c r="AF232" s="7"/>
     </row>
-    <row r="233" spans="1:32">
+    <row r="233" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A233" s="7"/>
       <c r="B233" s="7"/>
       <c r="C233" s="7"/>
@@ -24934,6 +24940,42 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="L8:Q8"/>
+    <mergeCell ref="L9:Q9"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="I24:Q25"/>
+    <mergeCell ref="I23:Q23"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="L10:Q10"/>
+    <mergeCell ref="I11:Q11"/>
+    <mergeCell ref="L12:Q12"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="L14:Q14"/>
+    <mergeCell ref="L15:Q15"/>
+    <mergeCell ref="L16:Q16"/>
+    <mergeCell ref="L18:Q18"/>
+    <mergeCell ref="G1:H77"/>
+    <mergeCell ref="L22:Q22"/>
+    <mergeCell ref="L26:L27"/>
+    <mergeCell ref="N26:N27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="L6:Q6"/>
+    <mergeCell ref="L7:Q7"/>
+    <mergeCell ref="B24:F25"/>
+    <mergeCell ref="I17:Q17"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="L19:Q19"/>
+    <mergeCell ref="L20:Q20"/>
+    <mergeCell ref="L21:Q21"/>
     <mergeCell ref="I2:Q4"/>
     <mergeCell ref="I5:Q5"/>
     <mergeCell ref="B23:F23"/>
@@ -24950,42 +24992,6 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B8:F10"/>
     <mergeCell ref="B11:F12"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="L19:Q19"/>
-    <mergeCell ref="L20:Q20"/>
-    <mergeCell ref="L21:Q21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="L14:Q14"/>
-    <mergeCell ref="L15:Q15"/>
-    <mergeCell ref="L16:Q16"/>
-    <mergeCell ref="L18:Q18"/>
-    <mergeCell ref="G1:H77"/>
-    <mergeCell ref="L22:Q22"/>
-    <mergeCell ref="L26:L27"/>
-    <mergeCell ref="N26:N27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="L6:Q6"/>
-    <mergeCell ref="L7:Q7"/>
-    <mergeCell ref="B24:F25"/>
-    <mergeCell ref="I17:Q17"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="L8:Q8"/>
-    <mergeCell ref="L9:Q9"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="I24:Q25"/>
-    <mergeCell ref="I23:Q23"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="O26:O27"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="L10:Q10"/>
-    <mergeCell ref="I11:Q11"/>
-    <mergeCell ref="L12:Q12"/>
-    <mergeCell ref="L13:Q13"/>
-    <mergeCell ref="M26:M27"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
